--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_소프트웨어팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_소프트웨어팀_입력_2026.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,8 +59,14 @@
       <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="002E7D32"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -112,8 +118,13 @@
         <fgColor rgb="008B1E22"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B08F36"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -179,11 +190,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -378,6 +403,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -606,13 +637,13 @@
 (직접 입력)</t>
       </text>
     </comment>
-    <comment ref="P4" authorId="0" shapeId="0">
+    <comment ref="R4" authorId="0" shapeId="0">
       <text>
         <t>▣ 상태
 (직접 입력)</t>
       </text>
     </comment>
-    <comment ref="Q4" authorId="0" shapeId="0">
+    <comment ref="S4" authorId="0" shapeId="0">
       <text>
         <t>▣ 메모
 (직접 입력)</t>
@@ -912,7 +943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q57"/>
+  <dimension ref="A1:S57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -930,8 +961,8 @@
     <col width="10" customWidth="1" style="55" min="13" max="13"/>
     <col width="8" customWidth="1" style="55" min="14" max="14"/>
     <col width="9" customWidth="1" style="55" min="15" max="15"/>
-    <col width="10" customWidth="1" style="55" min="16" max="16"/>
-    <col width="28" customWidth="1" style="55" min="17" max="17"/>
+    <col width="12" customWidth="1" style="55" min="16" max="16"/>
+    <col width="12" customWidth="1" style="55" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -954,8 +985,8 @@
       <c r="M1" s="16" t="n"/>
       <c r="N1" s="16" t="n"/>
       <c r="O1" s="16" t="n"/>
-      <c r="P1" s="16" t="n"/>
-      <c r="Q1" s="17" t="n"/>
+      <c r="R1" s="16" t="n"/>
+      <c r="S1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="63" t="inlineStr">
@@ -977,8 +1008,8 @@
       <c r="M2" s="16" t="n"/>
       <c r="N2" s="16" t="n"/>
       <c r="O2" s="16" t="n"/>
-      <c r="P2" s="17" t="n"/>
-      <c r="Q2" s="64" t="inlineStr">
+      <c r="R2" s="17" t="n"/>
+      <c r="S2" s="64" t="inlineStr">
         <is>
           <t>업데이트: 2026-05-02 01:42</t>
         </is>
@@ -1060,12 +1091,22 @@
           <t>✏입력</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr">
+      <c r="P3" s="65" t="inlineStr">
+        <is>
+          <t>✏입력</t>
+        </is>
+      </c>
+      <c r="Q3" s="65" t="inlineStr">
+        <is>
+          <t>✏입력</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
         <is>
           <t>✏선택▼</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="S3" s="4" t="inlineStr">
         <is>
           <t>✏메모</t>
         </is>
@@ -1147,12 +1188,24 @@
           <t>AUTORUN</t>
         </is>
       </c>
-      <c r="P4" s="7" t="inlineStr">
+      <c r="P4" s="66" t="inlineStr">
+        <is>
+          <t>제안서
+완료일</t>
+        </is>
+      </c>
+      <c r="Q4" s="66" t="inlineStr">
+        <is>
+          <t>설계
+완료일</t>
+        </is>
+      </c>
+      <c r="R4" s="7" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="Q4" s="7" t="inlineStr">
+      <c r="S4" s="7" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
@@ -1210,8 +1263,8 @@
       <c r="M5" s="11" t="n"/>
       <c r="N5" s="11" t="n"/>
       <c r="O5" s="11" t="n"/>
-      <c r="P5" s="9" t="n"/>
-      <c r="Q5" s="22" t="n"/>
+      <c r="R5" s="9" t="n"/>
+      <c r="S5" s="22" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="12" t="n">
@@ -1265,8 +1318,8 @@
       <c r="M6" s="15" t="n"/>
       <c r="N6" s="15" t="n"/>
       <c r="O6" s="15" t="n"/>
-      <c r="P6" s="13" t="n"/>
-      <c r="Q6" s="24" t="n"/>
+      <c r="R6" s="13" t="n"/>
+      <c r="S6" s="24" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="8" t="n">
@@ -1318,8 +1371,8 @@
       <c r="M7" s="11" t="n"/>
       <c r="N7" s="11" t="n"/>
       <c r="O7" s="11" t="n"/>
-      <c r="P7" s="9" t="n"/>
-      <c r="Q7" s="22" t="n"/>
+      <c r="R7" s="9" t="n"/>
+      <c r="S7" s="22" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="12" t="n">
@@ -1371,8 +1424,8 @@
       <c r="M8" s="15" t="n"/>
       <c r="N8" s="15" t="n"/>
       <c r="O8" s="15" t="n"/>
-      <c r="P8" s="13" t="n"/>
-      <c r="Q8" s="24" t="n"/>
+      <c r="R8" s="13" t="n"/>
+      <c r="S8" s="24" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="8" t="n">
@@ -1424,8 +1477,8 @@
       <c r="M9" s="11" t="n"/>
       <c r="N9" s="11" t="n"/>
       <c r="O9" s="11" t="n"/>
-      <c r="P9" s="9" t="n"/>
-      <c r="Q9" s="22" t="n"/>
+      <c r="R9" s="9" t="n"/>
+      <c r="S9" s="22" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="12" t="n">
@@ -1477,8 +1530,8 @@
       <c r="M10" s="15" t="n"/>
       <c r="N10" s="15" t="n"/>
       <c r="O10" s="15" t="n"/>
-      <c r="P10" s="13" t="n"/>
-      <c r="Q10" s="24" t="n"/>
+      <c r="R10" s="13" t="n"/>
+      <c r="S10" s="24" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="8" t="n">
@@ -1530,8 +1583,8 @@
       <c r="M11" s="11" t="n"/>
       <c r="N11" s="11" t="n"/>
       <c r="O11" s="11" t="n"/>
-      <c r="P11" s="9" t="n"/>
-      <c r="Q11" s="22" t="n"/>
+      <c r="R11" s="9" t="n"/>
+      <c r="S11" s="22" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="12" t="n">
@@ -1583,8 +1636,8 @@
       <c r="M12" s="15" t="n"/>
       <c r="N12" s="15" t="n"/>
       <c r="O12" s="15" t="n"/>
-      <c r="P12" s="13" t="n"/>
-      <c r="Q12" s="24" t="n"/>
+      <c r="R12" s="13" t="n"/>
+      <c r="S12" s="24" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="8" t="n">
@@ -1636,8 +1689,8 @@
       <c r="M13" s="11" t="n"/>
       <c r="N13" s="11" t="n"/>
       <c r="O13" s="11" t="n"/>
-      <c r="P13" s="9" t="n"/>
-      <c r="Q13" s="22" t="n"/>
+      <c r="R13" s="9" t="n"/>
+      <c r="S13" s="22" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="12" t="n">
@@ -1689,8 +1742,8 @@
       <c r="M14" s="15" t="n"/>
       <c r="N14" s="15" t="n"/>
       <c r="O14" s="15" t="n"/>
-      <c r="P14" s="13" t="n"/>
-      <c r="Q14" s="24" t="n"/>
+      <c r="R14" s="13" t="n"/>
+      <c r="S14" s="24" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="8" t="n">
@@ -1742,8 +1795,8 @@
       <c r="M15" s="11" t="n"/>
       <c r="N15" s="11" t="n"/>
       <c r="O15" s="11" t="n"/>
-      <c r="P15" s="9" t="n"/>
-      <c r="Q15" s="22" t="n"/>
+      <c r="R15" s="9" t="n"/>
+      <c r="S15" s="22" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="12" t="n">
@@ -1797,8 +1850,8 @@
       <c r="M16" s="15" t="n"/>
       <c r="N16" s="15" t="n"/>
       <c r="O16" s="15" t="n"/>
-      <c r="P16" s="13" t="n"/>
-      <c r="Q16" s="24" t="n"/>
+      <c r="R16" s="13" t="n"/>
+      <c r="S16" s="24" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="8" t="n">
@@ -1852,8 +1905,8 @@
       <c r="M17" s="11" t="n"/>
       <c r="N17" s="11" t="n"/>
       <c r="O17" s="11" t="n"/>
-      <c r="P17" s="9" t="n"/>
-      <c r="Q17" s="22" t="n"/>
+      <c r="R17" s="9" t="n"/>
+      <c r="S17" s="22" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="12" t="n">
@@ -1905,8 +1958,8 @@
       <c r="M18" s="15" t="n"/>
       <c r="N18" s="15" t="n"/>
       <c r="O18" s="15" t="n"/>
-      <c r="P18" s="13" t="n"/>
-      <c r="Q18" s="24" t="n"/>
+      <c r="R18" s="13" t="n"/>
+      <c r="S18" s="24" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="8" t="n">
@@ -1958,8 +2011,8 @@
       <c r="M19" s="11" t="n"/>
       <c r="N19" s="11" t="n"/>
       <c r="O19" s="11" t="n"/>
-      <c r="P19" s="9" t="n"/>
-      <c r="Q19" s="22" t="n"/>
+      <c r="R19" s="9" t="n"/>
+      <c r="S19" s="22" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="12" t="n">
@@ -2011,8 +2064,8 @@
       <c r="M20" s="15" t="n"/>
       <c r="N20" s="15" t="n"/>
       <c r="O20" s="15" t="n"/>
-      <c r="P20" s="13" t="n"/>
-      <c r="Q20" s="24" t="n"/>
+      <c r="R20" s="13" t="n"/>
+      <c r="S20" s="24" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="8" t="n">
@@ -2064,8 +2117,8 @@
       <c r="M21" s="11" t="n"/>
       <c r="N21" s="11" t="n"/>
       <c r="O21" s="11" t="n"/>
-      <c r="P21" s="9" t="n"/>
-      <c r="Q21" s="22" t="n"/>
+      <c r="R21" s="9" t="n"/>
+      <c r="S21" s="22" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="12" t="n">
@@ -2117,8 +2170,8 @@
       <c r="M22" s="15" t="n"/>
       <c r="N22" s="15" t="n"/>
       <c r="O22" s="15" t="n"/>
-      <c r="P22" s="13" t="n"/>
-      <c r="Q22" s="24" t="n"/>
+      <c r="R22" s="13" t="n"/>
+      <c r="S22" s="24" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="8" t="n">
@@ -2170,8 +2223,8 @@
       <c r="M23" s="11" t="n"/>
       <c r="N23" s="11" t="n"/>
       <c r="O23" s="11" t="n"/>
-      <c r="P23" s="9" t="n"/>
-      <c r="Q23" s="22" t="n"/>
+      <c r="R23" s="9" t="n"/>
+      <c r="S23" s="22" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="12" t="n">
@@ -2223,8 +2276,8 @@
       <c r="M24" s="15" t="n"/>
       <c r="N24" s="15" t="n"/>
       <c r="O24" s="15" t="n"/>
-      <c r="P24" s="13" t="n"/>
-      <c r="Q24" s="24" t="n"/>
+      <c r="R24" s="13" t="n"/>
+      <c r="S24" s="24" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="8" t="n">
@@ -2276,8 +2329,8 @@
       <c r="M25" s="11" t="n"/>
       <c r="N25" s="11" t="n"/>
       <c r="O25" s="11" t="n"/>
-      <c r="P25" s="9" t="n"/>
-      <c r="Q25" s="22" t="n"/>
+      <c r="R25" s="9" t="n"/>
+      <c r="S25" s="22" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="12" t="n">
@@ -2329,8 +2382,8 @@
       <c r="M26" s="15" t="n"/>
       <c r="N26" s="15" t="n"/>
       <c r="O26" s="15" t="n"/>
-      <c r="P26" s="13" t="n"/>
-      <c r="Q26" s="24" t="n"/>
+      <c r="R26" s="13" t="n"/>
+      <c r="S26" s="24" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="8" t="n">
@@ -2382,8 +2435,8 @@
       <c r="M27" s="11" t="n"/>
       <c r="N27" s="11" t="n"/>
       <c r="O27" s="11" t="n"/>
-      <c r="P27" s="9" t="n"/>
-      <c r="Q27" s="22" t="n"/>
+      <c r="R27" s="9" t="n"/>
+      <c r="S27" s="22" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="12" t="n"/>
@@ -2401,8 +2454,8 @@
       <c r="M28" s="13" t="n"/>
       <c r="N28" s="13" t="n"/>
       <c r="O28" s="13" t="n"/>
-      <c r="P28" s="13" t="n"/>
-      <c r="Q28" s="24" t="n"/>
+      <c r="R28" s="13" t="n"/>
+      <c r="S28" s="24" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="8" t="n"/>
@@ -2420,8 +2473,8 @@
       <c r="M29" s="9" t="n"/>
       <c r="N29" s="9" t="n"/>
       <c r="O29" s="9" t="n"/>
-      <c r="P29" s="9" t="n"/>
-      <c r="Q29" s="22" t="n"/>
+      <c r="R29" s="9" t="n"/>
+      <c r="S29" s="22" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="12" t="n"/>
@@ -2439,8 +2492,8 @@
       <c r="M30" s="13" t="n"/>
       <c r="N30" s="13" t="n"/>
       <c r="O30" s="13" t="n"/>
-      <c r="P30" s="13" t="n"/>
-      <c r="Q30" s="24" t="n"/>
+      <c r="R30" s="13" t="n"/>
+      <c r="S30" s="24" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="8" t="n"/>
@@ -2458,8 +2511,8 @@
       <c r="M31" s="9" t="n"/>
       <c r="N31" s="9" t="n"/>
       <c r="O31" s="9" t="n"/>
-      <c r="P31" s="9" t="n"/>
-      <c r="Q31" s="22" t="n"/>
+      <c r="R31" s="9" t="n"/>
+      <c r="S31" s="22" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="12" t="n"/>
@@ -2477,8 +2530,8 @@
       <c r="M32" s="13" t="n"/>
       <c r="N32" s="13" t="n"/>
       <c r="O32" s="13" t="n"/>
-      <c r="P32" s="13" t="n"/>
-      <c r="Q32" s="24" t="n"/>
+      <c r="R32" s="13" t="n"/>
+      <c r="S32" s="24" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="8" t="n"/>
@@ -2496,8 +2549,8 @@
       <c r="M33" s="9" t="n"/>
       <c r="N33" s="9" t="n"/>
       <c r="O33" s="9" t="n"/>
-      <c r="P33" s="9" t="n"/>
-      <c r="Q33" s="22" t="n"/>
+      <c r="R33" s="9" t="n"/>
+      <c r="S33" s="22" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="12" t="n"/>
@@ -2515,8 +2568,8 @@
       <c r="M34" s="13" t="n"/>
       <c r="N34" s="13" t="n"/>
       <c r="O34" s="13" t="n"/>
-      <c r="P34" s="13" t="n"/>
-      <c r="Q34" s="24" t="n"/>
+      <c r="R34" s="13" t="n"/>
+      <c r="S34" s="24" t="n"/>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="8" t="n"/>
@@ -2534,8 +2587,8 @@
       <c r="M35" s="9" t="n"/>
       <c r="N35" s="9" t="n"/>
       <c r="O35" s="9" t="n"/>
-      <c r="P35" s="9" t="n"/>
-      <c r="Q35" s="22" t="n"/>
+      <c r="R35" s="9" t="n"/>
+      <c r="S35" s="22" t="n"/>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="12" t="n"/>
@@ -2553,8 +2606,8 @@
       <c r="M36" s="13" t="n"/>
       <c r="N36" s="13" t="n"/>
       <c r="O36" s="13" t="n"/>
-      <c r="P36" s="13" t="n"/>
-      <c r="Q36" s="24" t="n"/>
+      <c r="R36" s="13" t="n"/>
+      <c r="S36" s="24" t="n"/>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="8" t="n"/>
@@ -2572,8 +2625,8 @@
       <c r="M37" s="9" t="n"/>
       <c r="N37" s="9" t="n"/>
       <c r="O37" s="9" t="n"/>
-      <c r="P37" s="9" t="n"/>
-      <c r="Q37" s="22" t="n"/>
+      <c r="R37" s="9" t="n"/>
+      <c r="S37" s="22" t="n"/>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="12" t="n"/>
@@ -2591,8 +2644,8 @@
       <c r="M38" s="13" t="n"/>
       <c r="N38" s="13" t="n"/>
       <c r="O38" s="13" t="n"/>
-      <c r="P38" s="13" t="n"/>
-      <c r="Q38" s="24" t="n"/>
+      <c r="R38" s="13" t="n"/>
+      <c r="S38" s="24" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="8" t="n"/>
@@ -2610,8 +2663,8 @@
       <c r="M39" s="9" t="n"/>
       <c r="N39" s="9" t="n"/>
       <c r="O39" s="9" t="n"/>
-      <c r="P39" s="9" t="n"/>
-      <c r="Q39" s="22" t="n"/>
+      <c r="R39" s="9" t="n"/>
+      <c r="S39" s="22" t="n"/>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="12" t="n"/>
@@ -2629,8 +2682,8 @@
       <c r="M40" s="13" t="n"/>
       <c r="N40" s="13" t="n"/>
       <c r="O40" s="13" t="n"/>
-      <c r="P40" s="13" t="n"/>
-      <c r="Q40" s="24" t="n"/>
+      <c r="R40" s="13" t="n"/>
+      <c r="S40" s="24" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="8" t="n"/>
@@ -2648,8 +2701,8 @@
       <c r="M41" s="9" t="n"/>
       <c r="N41" s="9" t="n"/>
       <c r="O41" s="9" t="n"/>
-      <c r="P41" s="9" t="n"/>
-      <c r="Q41" s="22" t="n"/>
+      <c r="R41" s="9" t="n"/>
+      <c r="S41" s="22" t="n"/>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="12" t="n"/>
@@ -2667,8 +2720,8 @@
       <c r="M42" s="13" t="n"/>
       <c r="N42" s="13" t="n"/>
       <c r="O42" s="13" t="n"/>
-      <c r="P42" s="13" t="n"/>
-      <c r="Q42" s="24" t="n"/>
+      <c r="R42" s="13" t="n"/>
+      <c r="S42" s="24" t="n"/>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="8" t="n"/>
@@ -2686,8 +2739,8 @@
       <c r="M43" s="9" t="n"/>
       <c r="N43" s="9" t="n"/>
       <c r="O43" s="9" t="n"/>
-      <c r="P43" s="9" t="n"/>
-      <c r="Q43" s="22" t="n"/>
+      <c r="R43" s="9" t="n"/>
+      <c r="S43" s="22" t="n"/>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="12" t="n"/>
@@ -2705,8 +2758,8 @@
       <c r="M44" s="13" t="n"/>
       <c r="N44" s="13" t="n"/>
       <c r="O44" s="13" t="n"/>
-      <c r="P44" s="13" t="n"/>
-      <c r="Q44" s="24" t="n"/>
+      <c r="R44" s="13" t="n"/>
+      <c r="S44" s="24" t="n"/>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="8" t="n"/>
@@ -2724,8 +2777,8 @@
       <c r="M45" s="9" t="n"/>
       <c r="N45" s="9" t="n"/>
       <c r="O45" s="9" t="n"/>
-      <c r="P45" s="9" t="n"/>
-      <c r="Q45" s="22" t="n"/>
+      <c r="R45" s="9" t="n"/>
+      <c r="S45" s="22" t="n"/>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="12" t="n"/>
@@ -2743,8 +2796,8 @@
       <c r="M46" s="13" t="n"/>
       <c r="N46" s="13" t="n"/>
       <c r="O46" s="13" t="n"/>
-      <c r="P46" s="13" t="n"/>
-      <c r="Q46" s="24" t="n"/>
+      <c r="R46" s="13" t="n"/>
+      <c r="S46" s="24" t="n"/>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="8" t="n"/>
@@ -2762,8 +2815,8 @@
       <c r="M47" s="9" t="n"/>
       <c r="N47" s="9" t="n"/>
       <c r="O47" s="9" t="n"/>
-      <c r="P47" s="9" t="n"/>
-      <c r="Q47" s="22" t="n"/>
+      <c r="R47" s="9" t="n"/>
+      <c r="S47" s="22" t="n"/>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="12" t="n"/>
@@ -2781,8 +2834,8 @@
       <c r="M48" s="13" t="n"/>
       <c r="N48" s="13" t="n"/>
       <c r="O48" s="13" t="n"/>
-      <c r="P48" s="13" t="n"/>
-      <c r="Q48" s="24" t="n"/>
+      <c r="R48" s="13" t="n"/>
+      <c r="S48" s="24" t="n"/>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="8" t="n"/>
@@ -2800,8 +2853,8 @@
       <c r="M49" s="9" t="n"/>
       <c r="N49" s="9" t="n"/>
       <c r="O49" s="9" t="n"/>
-      <c r="P49" s="9" t="n"/>
-      <c r="Q49" s="22" t="n"/>
+      <c r="R49" s="9" t="n"/>
+      <c r="S49" s="22" t="n"/>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="12" t="n"/>
@@ -2819,8 +2872,8 @@
       <c r="M50" s="13" t="n"/>
       <c r="N50" s="13" t="n"/>
       <c r="O50" s="13" t="n"/>
-      <c r="P50" s="13" t="n"/>
-      <c r="Q50" s="24" t="n"/>
+      <c r="R50" s="13" t="n"/>
+      <c r="S50" s="24" t="n"/>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="8" t="n"/>
@@ -2838,8 +2891,8 @@
       <c r="M51" s="9" t="n"/>
       <c r="N51" s="9" t="n"/>
       <c r="O51" s="9" t="n"/>
-      <c r="P51" s="9" t="n"/>
-      <c r="Q51" s="22" t="n"/>
+      <c r="R51" s="9" t="n"/>
+      <c r="S51" s="22" t="n"/>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="12" t="n"/>
@@ -2857,8 +2910,8 @@
       <c r="M52" s="13" t="n"/>
       <c r="N52" s="13" t="n"/>
       <c r="O52" s="13" t="n"/>
-      <c r="P52" s="13" t="n"/>
-      <c r="Q52" s="24" t="n"/>
+      <c r="R52" s="13" t="n"/>
+      <c r="S52" s="24" t="n"/>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="8" t="n"/>
@@ -2876,8 +2929,8 @@
       <c r="M53" s="9" t="n"/>
       <c r="N53" s="9" t="n"/>
       <c r="O53" s="9" t="n"/>
-      <c r="P53" s="9" t="n"/>
-      <c r="Q53" s="22" t="n"/>
+      <c r="R53" s="9" t="n"/>
+      <c r="S53" s="22" t="n"/>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="12" t="n"/>
@@ -2895,8 +2948,8 @@
       <c r="M54" s="13" t="n"/>
       <c r="N54" s="13" t="n"/>
       <c r="O54" s="13" t="n"/>
-      <c r="P54" s="13" t="n"/>
-      <c r="Q54" s="24" t="n"/>
+      <c r="R54" s="13" t="n"/>
+      <c r="S54" s="24" t="n"/>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="8" t="n"/>
@@ -2914,8 +2967,8 @@
       <c r="M55" s="9" t="n"/>
       <c r="N55" s="9" t="n"/>
       <c r="O55" s="9" t="n"/>
-      <c r="P55" s="9" t="n"/>
-      <c r="Q55" s="22" t="n"/>
+      <c r="R55" s="9" t="n"/>
+      <c r="S55" s="22" t="n"/>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="12" t="n"/>
@@ -2933,8 +2986,8 @@
       <c r="M56" s="13" t="n"/>
       <c r="N56" s="13" t="n"/>
       <c r="O56" s="13" t="n"/>
-      <c r="P56" s="13" t="n"/>
-      <c r="Q56" s="24" t="n"/>
+      <c r="R56" s="13" t="n"/>
+      <c r="S56" s="24" t="n"/>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="8" t="n"/>
@@ -2952,8 +3005,8 @@
       <c r="M57" s="9" t="n"/>
       <c r="N57" s="9" t="n"/>
       <c r="O57" s="9" t="n"/>
-      <c r="P57" s="9" t="n"/>
-      <c r="Q57" s="22" t="n"/>
+      <c r="R57" s="9" t="n"/>
+      <c r="S57" s="22" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_소프트웨어팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_소프트웨어팀_입력_2026.xlsx
@@ -208,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -408,6 +408,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -634,6 +646,20 @@
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
         <t>▣ AUTORUN
+(직접 입력)</t>
+      </text>
+    </comment>
+    <comment ref="P4" authorId="0" shapeId="0">
+      <text>
+        <t>▣ 제안서
+완료일
+(직접 입력)</t>
+      </text>
+    </comment>
+    <comment ref="Q4" authorId="0" shapeId="0">
+      <text>
+        <t>▣ 설계
+완료일
 (직접 입력)</t>
       </text>
     </comment>
@@ -963,10 +989,12 @@
     <col width="9" customWidth="1" style="55" min="15" max="15"/>
     <col width="12" customWidth="1" style="55" min="16" max="16"/>
     <col width="12" customWidth="1" style="55" min="17" max="17"/>
+    <col width="10" customWidth="1" style="55" min="18" max="18"/>
+    <col width="28" customWidth="1" style="55" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="62" t="inlineStr">
+      <c r="A1" s="67" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 소프트웨어팀 │ 2026</t>
         </is>
@@ -985,11 +1013,13 @@
       <c r="M1" s="16" t="n"/>
       <c r="N1" s="16" t="n"/>
       <c r="O1" s="16" t="n"/>
+      <c r="P1" s="16" t="n"/>
+      <c r="Q1" s="16" t="n"/>
       <c r="R1" s="16" t="n"/>
       <c r="S1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="63" t="inlineStr">
+      <c r="A2" s="68" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 소프트웨어팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1008,10 +1038,12 @@
       <c r="M2" s="16" t="n"/>
       <c r="N2" s="16" t="n"/>
       <c r="O2" s="16" t="n"/>
+      <c r="P2" s="16" t="n"/>
+      <c r="Q2" s="16" t="n"/>
       <c r="R2" s="17" t="n"/>
-      <c r="S2" s="64" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-02 01:42</t>
+      <c r="S2" s="69" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 00:45</t>
         </is>
       </c>
     </row>
@@ -1091,14 +1123,14 @@
           <t>✏입력</t>
         </is>
       </c>
-      <c r="P3" s="65" t="inlineStr">
-        <is>
-          <t>✏입력</t>
-        </is>
-      </c>
-      <c r="Q3" s="65" t="inlineStr">
-        <is>
-          <t>✏입력</t>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>PO후입력</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>PO후입력</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
@@ -1188,13 +1220,13 @@
           <t>AUTORUN</t>
         </is>
       </c>
-      <c r="P4" s="66" t="inlineStr">
+      <c r="P4" s="70" t="inlineStr">
         <is>
           <t>제안서
 완료일</t>
         </is>
       </c>
-      <c r="Q4" s="66" t="inlineStr">
+      <c r="Q4" s="70" t="inlineStr">
         <is>
           <t>설계
 완료일</t>
@@ -1263,6 +1295,8 @@
       <c r="M5" s="11" t="n"/>
       <c r="N5" s="11" t="n"/>
       <c r="O5" s="11" t="n"/>
+      <c r="P5" s="9" t="n"/>
+      <c r="Q5" s="9" t="n"/>
       <c r="R5" s="9" t="n"/>
       <c r="S5" s="22" t="n"/>
     </row>
@@ -1318,6 +1352,8 @@
       <c r="M6" s="15" t="n"/>
       <c r="N6" s="15" t="n"/>
       <c r="O6" s="15" t="n"/>
+      <c r="P6" s="13" t="n"/>
+      <c r="Q6" s="13" t="n"/>
       <c r="R6" s="13" t="n"/>
       <c r="S6" s="24" t="n"/>
     </row>
@@ -1371,6 +1407,8 @@
       <c r="M7" s="11" t="n"/>
       <c r="N7" s="11" t="n"/>
       <c r="O7" s="11" t="n"/>
+      <c r="P7" s="9" t="n"/>
+      <c r="Q7" s="9" t="n"/>
       <c r="R7" s="9" t="n"/>
       <c r="S7" s="22" t="n"/>
     </row>
@@ -1424,6 +1462,8 @@
       <c r="M8" s="15" t="n"/>
       <c r="N8" s="15" t="n"/>
       <c r="O8" s="15" t="n"/>
+      <c r="P8" s="13" t="n"/>
+      <c r="Q8" s="13" t="n"/>
       <c r="R8" s="13" t="n"/>
       <c r="S8" s="24" t="n"/>
     </row>
@@ -1477,6 +1517,8 @@
       <c r="M9" s="11" t="n"/>
       <c r="N9" s="11" t="n"/>
       <c r="O9" s="11" t="n"/>
+      <c r="P9" s="9" t="n"/>
+      <c r="Q9" s="9" t="n"/>
       <c r="R9" s="9" t="n"/>
       <c r="S9" s="22" t="n"/>
     </row>
@@ -1530,6 +1572,8 @@
       <c r="M10" s="15" t="n"/>
       <c r="N10" s="15" t="n"/>
       <c r="O10" s="15" t="n"/>
+      <c r="P10" s="13" t="n"/>
+      <c r="Q10" s="13" t="n"/>
       <c r="R10" s="13" t="n"/>
       <c r="S10" s="24" t="n"/>
     </row>
@@ -1583,6 +1627,8 @@
       <c r="M11" s="11" t="n"/>
       <c r="N11" s="11" t="n"/>
       <c r="O11" s="11" t="n"/>
+      <c r="P11" s="9" t="n"/>
+      <c r="Q11" s="9" t="n"/>
       <c r="R11" s="9" t="n"/>
       <c r="S11" s="22" t="n"/>
     </row>
@@ -1636,6 +1682,8 @@
       <c r="M12" s="15" t="n"/>
       <c r="N12" s="15" t="n"/>
       <c r="O12" s="15" t="n"/>
+      <c r="P12" s="13" t="n"/>
+      <c r="Q12" s="13" t="n"/>
       <c r="R12" s="13" t="n"/>
       <c r="S12" s="24" t="n"/>
     </row>
@@ -1689,6 +1737,8 @@
       <c r="M13" s="11" t="n"/>
       <c r="N13" s="11" t="n"/>
       <c r="O13" s="11" t="n"/>
+      <c r="P13" s="9" t="n"/>
+      <c r="Q13" s="9" t="n"/>
       <c r="R13" s="9" t="n"/>
       <c r="S13" s="22" t="n"/>
     </row>
@@ -1742,6 +1792,8 @@
       <c r="M14" s="15" t="n"/>
       <c r="N14" s="15" t="n"/>
       <c r="O14" s="15" t="n"/>
+      <c r="P14" s="13" t="n"/>
+      <c r="Q14" s="13" t="n"/>
       <c r="R14" s="13" t="n"/>
       <c r="S14" s="24" t="n"/>
     </row>
@@ -1795,6 +1847,8 @@
       <c r="M15" s="11" t="n"/>
       <c r="N15" s="11" t="n"/>
       <c r="O15" s="11" t="n"/>
+      <c r="P15" s="9" t="n"/>
+      <c r="Q15" s="9" t="n"/>
       <c r="R15" s="9" t="n"/>
       <c r="S15" s="22" t="n"/>
     </row>
@@ -1850,6 +1904,8 @@
       <c r="M16" s="15" t="n"/>
       <c r="N16" s="15" t="n"/>
       <c r="O16" s="15" t="n"/>
+      <c r="P16" s="13" t="n"/>
+      <c r="Q16" s="13" t="n"/>
       <c r="R16" s="13" t="n"/>
       <c r="S16" s="24" t="n"/>
     </row>
@@ -1905,6 +1961,8 @@
       <c r="M17" s="11" t="n"/>
       <c r="N17" s="11" t="n"/>
       <c r="O17" s="11" t="n"/>
+      <c r="P17" s="9" t="n"/>
+      <c r="Q17" s="9" t="n"/>
       <c r="R17" s="9" t="n"/>
       <c r="S17" s="22" t="n"/>
     </row>
@@ -1958,6 +2016,8 @@
       <c r="M18" s="15" t="n"/>
       <c r="N18" s="15" t="n"/>
       <c r="O18" s="15" t="n"/>
+      <c r="P18" s="13" t="n"/>
+      <c r="Q18" s="13" t="n"/>
       <c r="R18" s="13" t="n"/>
       <c r="S18" s="24" t="n"/>
     </row>
@@ -2011,6 +2071,8 @@
       <c r="M19" s="11" t="n"/>
       <c r="N19" s="11" t="n"/>
       <c r="O19" s="11" t="n"/>
+      <c r="P19" s="9" t="n"/>
+      <c r="Q19" s="9" t="n"/>
       <c r="R19" s="9" t="n"/>
       <c r="S19" s="22" t="n"/>
     </row>
@@ -2064,6 +2126,8 @@
       <c r="M20" s="15" t="n"/>
       <c r="N20" s="15" t="n"/>
       <c r="O20" s="15" t="n"/>
+      <c r="P20" s="13" t="n"/>
+      <c r="Q20" s="13" t="n"/>
       <c r="R20" s="13" t="n"/>
       <c r="S20" s="24" t="n"/>
     </row>
@@ -2117,6 +2181,8 @@
       <c r="M21" s="11" t="n"/>
       <c r="N21" s="11" t="n"/>
       <c r="O21" s="11" t="n"/>
+      <c r="P21" s="9" t="n"/>
+      <c r="Q21" s="9" t="n"/>
       <c r="R21" s="9" t="n"/>
       <c r="S21" s="22" t="n"/>
     </row>
@@ -2170,6 +2236,8 @@
       <c r="M22" s="15" t="n"/>
       <c r="N22" s="15" t="n"/>
       <c r="O22" s="15" t="n"/>
+      <c r="P22" s="13" t="n"/>
+      <c r="Q22" s="13" t="n"/>
       <c r="R22" s="13" t="n"/>
       <c r="S22" s="24" t="n"/>
     </row>
@@ -2223,6 +2291,8 @@
       <c r="M23" s="11" t="n"/>
       <c r="N23" s="11" t="n"/>
       <c r="O23" s="11" t="n"/>
+      <c r="P23" s="9" t="n"/>
+      <c r="Q23" s="9" t="n"/>
       <c r="R23" s="9" t="n"/>
       <c r="S23" s="22" t="n"/>
     </row>
@@ -2276,6 +2346,8 @@
       <c r="M24" s="15" t="n"/>
       <c r="N24" s="15" t="n"/>
       <c r="O24" s="15" t="n"/>
+      <c r="P24" s="13" t="n"/>
+      <c r="Q24" s="13" t="n"/>
       <c r="R24" s="13" t="n"/>
       <c r="S24" s="24" t="n"/>
     </row>
@@ -2329,6 +2401,8 @@
       <c r="M25" s="11" t="n"/>
       <c r="N25" s="11" t="n"/>
       <c r="O25" s="11" t="n"/>
+      <c r="P25" s="9" t="n"/>
+      <c r="Q25" s="9" t="n"/>
       <c r="R25" s="9" t="n"/>
       <c r="S25" s="22" t="n"/>
     </row>
@@ -2382,6 +2456,8 @@
       <c r="M26" s="15" t="n"/>
       <c r="N26" s="15" t="n"/>
       <c r="O26" s="15" t="n"/>
+      <c r="P26" s="13" t="n"/>
+      <c r="Q26" s="13" t="n"/>
       <c r="R26" s="13" t="n"/>
       <c r="S26" s="24" t="n"/>
     </row>
@@ -2435,6 +2511,8 @@
       <c r="M27" s="11" t="n"/>
       <c r="N27" s="11" t="n"/>
       <c r="O27" s="11" t="n"/>
+      <c r="P27" s="9" t="n"/>
+      <c r="Q27" s="9" t="n"/>
       <c r="R27" s="9" t="n"/>
       <c r="S27" s="22" t="n"/>
     </row>
@@ -2454,6 +2532,8 @@
       <c r="M28" s="13" t="n"/>
       <c r="N28" s="13" t="n"/>
       <c r="O28" s="13" t="n"/>
+      <c r="P28" s="13" t="n"/>
+      <c r="Q28" s="13" t="n"/>
       <c r="R28" s="13" t="n"/>
       <c r="S28" s="24" t="n"/>
     </row>
@@ -2473,6 +2553,8 @@
       <c r="M29" s="9" t="n"/>
       <c r="N29" s="9" t="n"/>
       <c r="O29" s="9" t="n"/>
+      <c r="P29" s="9" t="n"/>
+      <c r="Q29" s="9" t="n"/>
       <c r="R29" s="9" t="n"/>
       <c r="S29" s="22" t="n"/>
     </row>
@@ -2492,6 +2574,8 @@
       <c r="M30" s="13" t="n"/>
       <c r="N30" s="13" t="n"/>
       <c r="O30" s="13" t="n"/>
+      <c r="P30" s="13" t="n"/>
+      <c r="Q30" s="13" t="n"/>
       <c r="R30" s="13" t="n"/>
       <c r="S30" s="24" t="n"/>
     </row>
@@ -2511,6 +2595,8 @@
       <c r="M31" s="9" t="n"/>
       <c r="N31" s="9" t="n"/>
       <c r="O31" s="9" t="n"/>
+      <c r="P31" s="9" t="n"/>
+      <c r="Q31" s="9" t="n"/>
       <c r="R31" s="9" t="n"/>
       <c r="S31" s="22" t="n"/>
     </row>
@@ -2530,6 +2616,8 @@
       <c r="M32" s="13" t="n"/>
       <c r="N32" s="13" t="n"/>
       <c r="O32" s="13" t="n"/>
+      <c r="P32" s="13" t="n"/>
+      <c r="Q32" s="13" t="n"/>
       <c r="R32" s="13" t="n"/>
       <c r="S32" s="24" t="n"/>
     </row>
@@ -2549,6 +2637,8 @@
       <c r="M33" s="9" t="n"/>
       <c r="N33" s="9" t="n"/>
       <c r="O33" s="9" t="n"/>
+      <c r="P33" s="9" t="n"/>
+      <c r="Q33" s="9" t="n"/>
       <c r="R33" s="9" t="n"/>
       <c r="S33" s="22" t="n"/>
     </row>
@@ -2568,6 +2658,8 @@
       <c r="M34" s="13" t="n"/>
       <c r="N34" s="13" t="n"/>
       <c r="O34" s="13" t="n"/>
+      <c r="P34" s="13" t="n"/>
+      <c r="Q34" s="13" t="n"/>
       <c r="R34" s="13" t="n"/>
       <c r="S34" s="24" t="n"/>
     </row>
@@ -2587,6 +2679,8 @@
       <c r="M35" s="9" t="n"/>
       <c r="N35" s="9" t="n"/>
       <c r="O35" s="9" t="n"/>
+      <c r="P35" s="9" t="n"/>
+      <c r="Q35" s="9" t="n"/>
       <c r="R35" s="9" t="n"/>
       <c r="S35" s="22" t="n"/>
     </row>
@@ -2606,6 +2700,8 @@
       <c r="M36" s="13" t="n"/>
       <c r="N36" s="13" t="n"/>
       <c r="O36" s="13" t="n"/>
+      <c r="P36" s="13" t="n"/>
+      <c r="Q36" s="13" t="n"/>
       <c r="R36" s="13" t="n"/>
       <c r="S36" s="24" t="n"/>
     </row>
@@ -2625,6 +2721,8 @@
       <c r="M37" s="9" t="n"/>
       <c r="N37" s="9" t="n"/>
       <c r="O37" s="9" t="n"/>
+      <c r="P37" s="9" t="n"/>
+      <c r="Q37" s="9" t="n"/>
       <c r="R37" s="9" t="n"/>
       <c r="S37" s="22" t="n"/>
     </row>
@@ -2644,6 +2742,8 @@
       <c r="M38" s="13" t="n"/>
       <c r="N38" s="13" t="n"/>
       <c r="O38" s="13" t="n"/>
+      <c r="P38" s="13" t="n"/>
+      <c r="Q38" s="13" t="n"/>
       <c r="R38" s="13" t="n"/>
       <c r="S38" s="24" t="n"/>
     </row>
@@ -2663,6 +2763,8 @@
       <c r="M39" s="9" t="n"/>
       <c r="N39" s="9" t="n"/>
       <c r="O39" s="9" t="n"/>
+      <c r="P39" s="9" t="n"/>
+      <c r="Q39" s="9" t="n"/>
       <c r="R39" s="9" t="n"/>
       <c r="S39" s="22" t="n"/>
     </row>
@@ -2682,6 +2784,8 @@
       <c r="M40" s="13" t="n"/>
       <c r="N40" s="13" t="n"/>
       <c r="O40" s="13" t="n"/>
+      <c r="P40" s="13" t="n"/>
+      <c r="Q40" s="13" t="n"/>
       <c r="R40" s="13" t="n"/>
       <c r="S40" s="24" t="n"/>
     </row>
@@ -2701,6 +2805,8 @@
       <c r="M41" s="9" t="n"/>
       <c r="N41" s="9" t="n"/>
       <c r="O41" s="9" t="n"/>
+      <c r="P41" s="9" t="n"/>
+      <c r="Q41" s="9" t="n"/>
       <c r="R41" s="9" t="n"/>
       <c r="S41" s="22" t="n"/>
     </row>
@@ -2720,6 +2826,8 @@
       <c r="M42" s="13" t="n"/>
       <c r="N42" s="13" t="n"/>
       <c r="O42" s="13" t="n"/>
+      <c r="P42" s="13" t="n"/>
+      <c r="Q42" s="13" t="n"/>
       <c r="R42" s="13" t="n"/>
       <c r="S42" s="24" t="n"/>
     </row>
@@ -2739,6 +2847,8 @@
       <c r="M43" s="9" t="n"/>
       <c r="N43" s="9" t="n"/>
       <c r="O43" s="9" t="n"/>
+      <c r="P43" s="9" t="n"/>
+      <c r="Q43" s="9" t="n"/>
       <c r="R43" s="9" t="n"/>
       <c r="S43" s="22" t="n"/>
     </row>
@@ -2758,6 +2868,8 @@
       <c r="M44" s="13" t="n"/>
       <c r="N44" s="13" t="n"/>
       <c r="O44" s="13" t="n"/>
+      <c r="P44" s="13" t="n"/>
+      <c r="Q44" s="13" t="n"/>
       <c r="R44" s="13" t="n"/>
       <c r="S44" s="24" t="n"/>
     </row>
@@ -2777,6 +2889,8 @@
       <c r="M45" s="9" t="n"/>
       <c r="N45" s="9" t="n"/>
       <c r="O45" s="9" t="n"/>
+      <c r="P45" s="9" t="n"/>
+      <c r="Q45" s="9" t="n"/>
       <c r="R45" s="9" t="n"/>
       <c r="S45" s="22" t="n"/>
     </row>
@@ -2796,6 +2910,8 @@
       <c r="M46" s="13" t="n"/>
       <c r="N46" s="13" t="n"/>
       <c r="O46" s="13" t="n"/>
+      <c r="P46" s="13" t="n"/>
+      <c r="Q46" s="13" t="n"/>
       <c r="R46" s="13" t="n"/>
       <c r="S46" s="24" t="n"/>
     </row>
@@ -2815,6 +2931,8 @@
       <c r="M47" s="9" t="n"/>
       <c r="N47" s="9" t="n"/>
       <c r="O47" s="9" t="n"/>
+      <c r="P47" s="9" t="n"/>
+      <c r="Q47" s="9" t="n"/>
       <c r="R47" s="9" t="n"/>
       <c r="S47" s="22" t="n"/>
     </row>
@@ -2834,6 +2952,8 @@
       <c r="M48" s="13" t="n"/>
       <c r="N48" s="13" t="n"/>
       <c r="O48" s="13" t="n"/>
+      <c r="P48" s="13" t="n"/>
+      <c r="Q48" s="13" t="n"/>
       <c r="R48" s="13" t="n"/>
       <c r="S48" s="24" t="n"/>
     </row>
@@ -2853,6 +2973,8 @@
       <c r="M49" s="9" t="n"/>
       <c r="N49" s="9" t="n"/>
       <c r="O49" s="9" t="n"/>
+      <c r="P49" s="9" t="n"/>
+      <c r="Q49" s="9" t="n"/>
       <c r="R49" s="9" t="n"/>
       <c r="S49" s="22" t="n"/>
     </row>
@@ -2872,6 +2994,8 @@
       <c r="M50" s="13" t="n"/>
       <c r="N50" s="13" t="n"/>
       <c r="O50" s="13" t="n"/>
+      <c r="P50" s="13" t="n"/>
+      <c r="Q50" s="13" t="n"/>
       <c r="R50" s="13" t="n"/>
       <c r="S50" s="24" t="n"/>
     </row>
@@ -2891,6 +3015,8 @@
       <c r="M51" s="9" t="n"/>
       <c r="N51" s="9" t="n"/>
       <c r="O51" s="9" t="n"/>
+      <c r="P51" s="9" t="n"/>
+      <c r="Q51" s="9" t="n"/>
       <c r="R51" s="9" t="n"/>
       <c r="S51" s="22" t="n"/>
     </row>
@@ -2910,6 +3036,8 @@
       <c r="M52" s="13" t="n"/>
       <c r="N52" s="13" t="n"/>
       <c r="O52" s="13" t="n"/>
+      <c r="P52" s="13" t="n"/>
+      <c r="Q52" s="13" t="n"/>
       <c r="R52" s="13" t="n"/>
       <c r="S52" s="24" t="n"/>
     </row>
@@ -2929,6 +3057,8 @@
       <c r="M53" s="9" t="n"/>
       <c r="N53" s="9" t="n"/>
       <c r="O53" s="9" t="n"/>
+      <c r="P53" s="9" t="n"/>
+      <c r="Q53" s="9" t="n"/>
       <c r="R53" s="9" t="n"/>
       <c r="S53" s="22" t="n"/>
     </row>
@@ -2948,6 +3078,8 @@
       <c r="M54" s="13" t="n"/>
       <c r="N54" s="13" t="n"/>
       <c r="O54" s="13" t="n"/>
+      <c r="P54" s="13" t="n"/>
+      <c r="Q54" s="13" t="n"/>
       <c r="R54" s="13" t="n"/>
       <c r="S54" s="24" t="n"/>
     </row>
@@ -2967,6 +3099,8 @@
       <c r="M55" s="9" t="n"/>
       <c r="N55" s="9" t="n"/>
       <c r="O55" s="9" t="n"/>
+      <c r="P55" s="9" t="n"/>
+      <c r="Q55" s="9" t="n"/>
       <c r="R55" s="9" t="n"/>
       <c r="S55" s="22" t="n"/>
     </row>
@@ -2986,6 +3120,8 @@
       <c r="M56" s="13" t="n"/>
       <c r="N56" s="13" t="n"/>
       <c r="O56" s="13" t="n"/>
+      <c r="P56" s="13" t="n"/>
+      <c r="Q56" s="13" t="n"/>
       <c r="R56" s="13" t="n"/>
       <c r="S56" s="24" t="n"/>
     </row>
@@ -3005,14 +3141,16 @@
       <c r="M57" s="9" t="n"/>
       <c r="N57" s="9" t="n"/>
       <c r="O57" s="9" t="n"/>
+      <c r="P57" s="9" t="n"/>
+      <c r="Q57" s="9" t="n"/>
       <c r="R57" s="9" t="n"/>
       <c r="S57" s="22" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="A2:P2"/>
+    <mergeCell ref="A2:R2"/>
+    <mergeCell ref="A1:S1"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="P5:P28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_소프트웨어팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_소프트웨어팀_입력_2026.xlsx
@@ -208,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -421,6 +421,24 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -612,8 +630,11 @@
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 담당자
-(직접 입력)</t>
+        <t>▣ 부서 담당자
+• 부서 내 실제 담당자 이름 입력
+  예: 정민규, 한재운, 이찬
+• 입력 시: PMS에도 자동 반영
+• 빈 칸: 부서 참여 확정, 담당자 미정</t>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
@@ -627,52 +648,89 @@
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 검토
-(직접 입력)</t>
+        <t>▣ 검토 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 프로그램
-(직접 입력)</t>
+        <t>▣ 프로그램 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>▣ DRYRUN
-(직접 입력)</t>
+        <t>▣ DRYRUN (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>▣ AUTORUN
-(직접 입력)</t>
+        <t>▣ AUTORUN (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 제안서
-완료일
-(직접 입력)</t>
+        <t>▣ 제안서 완료일
+★ 날짜 입력 (% 아님 ⚠️)
+• 형식: YYYY-MM-DD  예: 2026-05-15
+• 허용: 26-5-15, 260515, 2026.5.15 (자동 정규화)
+• 실제 제안서 작성·제출 완료된 날짜 기입
+• 비워두면 미완료 상태
+• 예정일이 아닌 ★실제 완료일★ 만 입력</t>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 설계
-완료일
-(직접 입력)</t>
+        <t>▣ 설계 완료일 (3D/2D 설계 완료)
+★ 날짜 입력 (% 아님 ⚠️)
+• 형식: YYYY-MM-DD  예: 2026-06-30
+• 3D/2D 설계가 실제로 완료된 날짜
+• 비워두면 미완료
+• 예정일 아닌 실제 완료일</t>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 상태
-(직접 입력)</t>
+        <t>▣ 부서 작업 상태
+• 드롭다운 선택:
+  미착수 — 작업 시작 안 함
+  진행중 — 작업 진행 중
+  완료   — 부서 작업 완료
+  N/A    — 해당 부서 무관 프로젝트
+• 부서장이 매주 상태 갱신 권장</t>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 메모
-(직접 입력)</t>
+        <t>▣ 메모 (부서 자유 입력)
+• 자유 텍스트 입력
+• 활용:
+  - 이슈사항 (예: 자재 결품, 외주 지연)
+  - 변경 요청 (예: 사양 변경, 납기 조정)
+  - 다른 부서·PM에게 공유할 정보
+• 대시보드 집계에는 미포함</t>
       </text>
     </comment>
   </commentList>
@@ -994,7 +1052,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="67" t="inlineStr">
+      <c r="A1" s="74" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 소프트웨어팀 │ 2026</t>
         </is>
@@ -1019,7 +1077,7 @@
       <c r="S1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="68" t="inlineStr">
+      <c r="A2" s="75" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 소프트웨어팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1041,9 +1099,9 @@
       <c r="P2" s="16" t="n"/>
       <c r="Q2" s="16" t="n"/>
       <c r="R2" s="17" t="n"/>
-      <c r="S2" s="69" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 00:45</t>
+      <c r="S2" s="76" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 01:07</t>
         </is>
       </c>
     </row>

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_소프트웨어팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_소프트웨어팀_입력_2026.xlsx
@@ -208,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -421,6 +421,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1052,7 +1061,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="74" t="inlineStr">
+      <c r="A1" s="77" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 소프트웨어팀 │ 2026</t>
         </is>
@@ -1077,7 +1086,7 @@
       <c r="S1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="75" t="inlineStr">
+      <c r="A2" s="78" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 소프트웨어팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1099,9 +1108,9 @@
       <c r="P2" s="16" t="n"/>
       <c r="Q2" s="16" t="n"/>
       <c r="R2" s="17" t="n"/>
-      <c r="S2" s="76" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 01:07</t>
+      <c r="S2" s="79" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 02:01</t>
         </is>
       </c>
     </row>

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_소프트웨어팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_소프트웨어팀_입력_2026.xlsx
@@ -208,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -421,6 +421,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -648,11 +657,15 @@
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 전체 진척률(%)
-• 자동 계산 — 참여 부서 소계의 평균
-  예: 3개 부서 진척률 80/50/30 → 53%
-• sync 시 갱신, 수동 수정 불가
-• 100% = 전 부서 완료 상태</t>
+        <t>▣ 부서 진척률 (%) — 본인 부서 작업
+• 자동 계산 (수정 불가, sync 시 갱신)
+• 시작일·완료일 입력 기반:
+    0%  = 미착수    (시작일·완료일 모두 빈 칸)
+   50%  = 진행중    (시작일만 입력)
+  100%  = 완료      (완료일까지 입력)
+• ★ 이 값은 '이 부서'만의 진척률입니다.
+• 프로젝트 전체 진척률은 PMS 1_프로젝트등록
+  '진척률(%)' 컬럼에서 확인 (= 완료부서/참여부서)</t>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
@@ -1061,7 +1074,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="77" t="inlineStr">
+      <c r="A1" s="80" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 소프트웨어팀 │ 2026</t>
         </is>
@@ -1086,7 +1099,7 @@
       <c r="S1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="78" t="inlineStr">
+      <c r="A2" s="81" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 소프트웨어팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1108,9 +1121,9 @@
       <c r="P2" s="16" t="n"/>
       <c r="Q2" s="16" t="n"/>
       <c r="R2" s="17" t="n"/>
-      <c r="S2" s="79" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 02:01</t>
+      <c r="S2" s="82" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 11:54</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1277,7 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>전체진척률(%)</t>
+          <t>부서진척률(%)</t>
         </is>
       </c>
       <c r="L4" s="7" t="inlineStr">

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_소프트웨어팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_소프트웨어팀_입력_2026.xlsx
@@ -1369,7 +1369,7 @@
       </c>
       <c r="J5" s="9" t="n"/>
       <c r="K5" s="10" t="n">
-        <v>0.009166666666666667</v>
+        <v>0</v>
       </c>
       <c r="L5" s="11" t="n"/>
       <c r="M5" s="11" t="n"/>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="J6" s="13" t="n"/>
       <c r="K6" s="14" t="n">
-        <v>0.007800000000000001</v>
+        <v>0</v>
       </c>
       <c r="L6" s="15" t="n"/>
       <c r="M6" s="15" t="n"/>
@@ -1482,7 +1482,9 @@
         </is>
       </c>
       <c r="J7" s="9" t="n"/>
-      <c r="K7" s="10" t="inlineStr"/>
+      <c r="K7" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L7" s="11" t="n"/>
       <c r="M7" s="11" t="n"/>
       <c r="N7" s="11" t="n"/>
@@ -1537,7 +1539,9 @@
         </is>
       </c>
       <c r="J8" s="13" t="n"/>
-      <c r="K8" s="14" t="inlineStr"/>
+      <c r="K8" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L8" s="15" t="n"/>
       <c r="M8" s="15" t="n"/>
       <c r="N8" s="15" t="n"/>
@@ -1592,7 +1596,9 @@
         </is>
       </c>
       <c r="J9" s="9" t="n"/>
-      <c r="K9" s="10" t="inlineStr"/>
+      <c r="K9" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L9" s="11" t="n"/>
       <c r="M9" s="11" t="n"/>
       <c r="N9" s="11" t="n"/>
@@ -1647,7 +1653,9 @@
         </is>
       </c>
       <c r="J10" s="13" t="n"/>
-      <c r="K10" s="14" t="inlineStr"/>
+      <c r="K10" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L10" s="15" t="n"/>
       <c r="M10" s="15" t="n"/>
       <c r="N10" s="15" t="n"/>
@@ -1702,7 +1710,9 @@
         </is>
       </c>
       <c r="J11" s="9" t="n"/>
-      <c r="K11" s="10" t="inlineStr"/>
+      <c r="K11" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L11" s="11" t="n"/>
       <c r="M11" s="11" t="n"/>
       <c r="N11" s="11" t="n"/>
@@ -1757,7 +1767,9 @@
         </is>
       </c>
       <c r="J12" s="13" t="n"/>
-      <c r="K12" s="14" t="inlineStr"/>
+      <c r="K12" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15" t="n"/>
       <c r="N12" s="15" t="n"/>
@@ -1812,7 +1824,9 @@
         </is>
       </c>
       <c r="J13" s="9" t="n"/>
-      <c r="K13" s="10" t="inlineStr"/>
+      <c r="K13" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L13" s="11" t="n"/>
       <c r="M13" s="11" t="n"/>
       <c r="N13" s="11" t="n"/>
@@ -1867,7 +1881,9 @@
         </is>
       </c>
       <c r="J14" s="13" t="n"/>
-      <c r="K14" s="14" t="inlineStr"/>
+      <c r="K14" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L14" s="15" t="n"/>
       <c r="M14" s="15" t="n"/>
       <c r="N14" s="15" t="n"/>
@@ -1922,7 +1938,9 @@
         </is>
       </c>
       <c r="J15" s="9" t="n"/>
-      <c r="K15" s="10" t="inlineStr"/>
+      <c r="K15" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L15" s="11" t="n"/>
       <c r="M15" s="11" t="n"/>
       <c r="N15" s="11" t="n"/>
@@ -1978,7 +1996,7 @@
       </c>
       <c r="J16" s="13" t="n"/>
       <c r="K16" s="14" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="L16" s="15" t="n"/>
       <c r="M16" s="15" t="n"/>
@@ -2035,7 +2053,7 @@
       </c>
       <c r="J17" s="9" t="n"/>
       <c r="K17" s="10" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="L17" s="11" t="n"/>
       <c r="M17" s="11" t="n"/>
@@ -2091,7 +2109,9 @@
         </is>
       </c>
       <c r="J18" s="13" t="n"/>
-      <c r="K18" s="14" t="inlineStr"/>
+      <c r="K18" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L18" s="15" t="n"/>
       <c r="M18" s="15" t="n"/>
       <c r="N18" s="15" t="n"/>
@@ -2146,7 +2166,9 @@
         </is>
       </c>
       <c r="J19" s="9" t="n"/>
-      <c r="K19" s="10" t="inlineStr"/>
+      <c r="K19" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L19" s="11" t="n"/>
       <c r="M19" s="11" t="n"/>
       <c r="N19" s="11" t="n"/>
@@ -2201,7 +2223,9 @@
         </is>
       </c>
       <c r="J20" s="13" t="n"/>
-      <c r="K20" s="14" t="inlineStr"/>
+      <c r="K20" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L20" s="15" t="n"/>
       <c r="M20" s="15" t="n"/>
       <c r="N20" s="15" t="n"/>
@@ -2256,7 +2280,9 @@
         </is>
       </c>
       <c r="J21" s="9" t="n"/>
-      <c r="K21" s="10" t="inlineStr"/>
+      <c r="K21" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L21" s="11" t="n"/>
       <c r="M21" s="11" t="n"/>
       <c r="N21" s="11" t="n"/>
@@ -2311,7 +2337,9 @@
         </is>
       </c>
       <c r="J22" s="13" t="n"/>
-      <c r="K22" s="14" t="inlineStr"/>
+      <c r="K22" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L22" s="15" t="n"/>
       <c r="M22" s="15" t="n"/>
       <c r="N22" s="15" t="n"/>
@@ -2366,7 +2394,9 @@
         </is>
       </c>
       <c r="J23" s="9" t="n"/>
-      <c r="K23" s="10" t="inlineStr"/>
+      <c r="K23" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L23" s="11" t="n"/>
       <c r="M23" s="11" t="n"/>
       <c r="N23" s="11" t="n"/>
@@ -2421,7 +2451,9 @@
         </is>
       </c>
       <c r="J24" s="13" t="n"/>
-      <c r="K24" s="14" t="inlineStr"/>
+      <c r="K24" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L24" s="15" t="n"/>
       <c r="M24" s="15" t="n"/>
       <c r="N24" s="15" t="n"/>
@@ -2476,7 +2508,9 @@
         </is>
       </c>
       <c r="J25" s="9" t="n"/>
-      <c r="K25" s="10" t="inlineStr"/>
+      <c r="K25" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L25" s="11" t="n"/>
       <c r="M25" s="11" t="n"/>
       <c r="N25" s="11" t="n"/>
@@ -2531,7 +2565,9 @@
         </is>
       </c>
       <c r="J26" s="13" t="n"/>
-      <c r="K26" s="14" t="inlineStr"/>
+      <c r="K26" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L26" s="15" t="n"/>
       <c r="M26" s="15" t="n"/>
       <c r="N26" s="15" t="n"/>
@@ -2586,7 +2622,9 @@
         </is>
       </c>
       <c r="J27" s="9" t="n"/>
-      <c r="K27" s="10" t="inlineStr"/>
+      <c r="K27" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L27" s="11" t="n"/>
       <c r="M27" s="11" t="n"/>
       <c r="N27" s="11" t="n"/>

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_소프트웨어팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_소프트웨어팀_입력_2026.xlsx
@@ -208,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -421,6 +421,24 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -542,15 +560,30 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -564,46 +597,86 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 모델 (장비 모델명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ PO유형 (발주 성격)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -614,11 +687,19 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
+        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 영업단계 (Sales Pipeline)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -633,31 +714,55 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
+        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 진행상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
+        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 담당자
 • 부서 내 실제 담당자 이름 입력
   예: 정민규, 한재운, 이찬
 • 입력 시: PMS에도 자동 반영
 • 빈 칸: 부서 참여 확정, 담당자 미정</t>
+        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 진척률 (%) — 본인 부서 작업
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 진척률 (%) — 본인 부서 작업
 • 자동 계산 (수정 불가, sync 시 갱신)
 • 시작일·완료일 입력 기반:
     0%  = 미착수    (시작일·완료일 모두 빈 칸)
@@ -666,93 +771,158 @@
 • ★ 이 값은 '이 부서'만의 진척률입니다.
 • 프로젝트 전체 진척률은 PMS 1_프로젝트등록
   '진척률(%)' 컬럼에서 확인 (= 완료부서/참여부서)</t>
+        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 검토 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 검토 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 프로그램 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 프로그램 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>▣ DRYRUN (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ DRYRUN (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>▣ AUTORUN (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ AUTORUN (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 제안서 완료일
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 제안서 완료일
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD  예: 2026-05-15
 • 허용: 26-5-15, 260515, 2026.5.15 (자동 정규화)
 • 실제 제안서 작성·제출 완료된 날짜 기입
 • 비워두면 미완료 상태
 • 예정일이 아닌 ★실제 완료일★ 만 입력</t>
+        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 설계 완료일 (3D/2D 설계 완료)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 설계 완료일 (3D/2D 설계 완료)
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD  예: 2026-06-30
 • 3D/2D 설계가 실제로 완료된 날짜
 • 비워두면 미완료
 • 예정일 아닌 실제 완료일</t>
+        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 작업 상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 작업 상태
 • 드롭다운 선택:
   미착수 — 작업 시작 안 함
   진행중 — 작업 진행 중
   완료   — 부서 작업 완료
   N/A    — 해당 부서 무관 프로젝트
 • 부서장이 매주 상태 갱신 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 메모 (부서 자유 입력)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 메모 (부서 자유 입력)
 • 자유 텍스트 입력
 • 활용:
   - 이슈사항 (예: 자재 결품, 외주 지연)
   - 변경 요청 (예: 사양 변경, 납기 조정)
   - 다른 부서·PM에게 공유할 정보
 • 대시보드 집계에는 미포함</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -1074,7 +1244,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="80" t="inlineStr">
+      <c r="A1" s="86" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 소프트웨어팀 │ 2026</t>
         </is>
@@ -1099,7 +1269,7 @@
       <c r="S1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="81" t="inlineStr">
+      <c r="A2" s="87" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 소프트웨어팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1121,9 +1291,9 @@
       <c r="P2" s="16" t="n"/>
       <c r="Q2" s="16" t="n"/>
       <c r="R2" s="17" t="n"/>
-      <c r="S2" s="82" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 11:54</t>
+      <c r="S2" s="88" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:34</t>
         </is>
       </c>
     </row>

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_소프트웨어팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_소프트웨어팀_입력_2026.xlsx
@@ -124,7 +124,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -204,11 +204,40 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -476,6 +505,17 @@
     <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1244,7 +1284,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="86" t="inlineStr">
+      <c r="A1" s="89" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 소프트웨어팀 │ 2026</t>
         </is>
@@ -1269,7 +1309,7 @@
       <c r="S1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="87" t="inlineStr">
+      <c r="A2" s="90" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 소프트웨어팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1288,14 +1328,14 @@
       <c r="M2" s="16" t="n"/>
       <c r="N2" s="16" t="n"/>
       <c r="O2" s="16" t="n"/>
-      <c r="P2" s="16" t="n"/>
-      <c r="Q2" s="16" t="n"/>
-      <c r="R2" s="17" t="n"/>
-      <c r="S2" s="88" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:34</t>
-        </is>
-      </c>
+      <c r="P2" s="17" t="n"/>
+      <c r="Q2" s="91" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:56</t>
+        </is>
+      </c>
+      <c r="R2" s="92" t="n"/>
+      <c r="S2" s="93" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -3436,9 +3476,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2:R2"/>
+  <mergeCells count="3">
+    <mergeCell ref="Q2:S2"/>
     <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A2:P2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="P5:P28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_소프트웨어팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_소프트웨어팀_입력_2026.xlsx
@@ -237,7 +237,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -516,6 +516,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -600,30 +609,15 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ NO (일련번호)
+        <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
-        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 관리코드 (프로젝트 고유 번호)
+        <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -637,86 +631,46 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주번호
+        <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
-        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 고객사 (거래처명)
+        <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 모델 (장비 모델명)
+        <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
-        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
-        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ PO유형 (발주 성격)
+        <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -727,19 +681,11 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
-        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 영업단계 (Sales Pipeline)
+        <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -754,55 +700,31 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
-        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 진행상태
+        <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
-        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서 담당자
+        <t>▣ 부서 담당자
 • 부서 내 실제 담당자 이름 입력
   예: 정민규, 한재운, 이찬
 • 입력 시: PMS에도 자동 반영
 • 빈 칸: 부서 참여 확정, 담당자 미정</t>
-        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서 진척률 (%) — 본인 부서 작업
+        <t>▣ 부서 진척률 (%) — 본인 부서 작업
 • 자동 계산 (수정 불가, sync 시 갱신)
 • 시작일·완료일 입력 기반:
     0%  = 미착수    (시작일·완료일 모두 빈 칸)
@@ -811,158 +733,113 @@
 • ★ 이 값은 '이 부서'만의 진척률입니다.
 • 프로젝트 전체 진척률은 PMS 1_프로젝트등록
   '진척률(%)' 컬럼에서 확인 (= 완료부서/참여부서)</t>
-        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 검토 (세부항목 진척률)
+        <t>▣ 검토 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-        </r>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 프로그램 (세부항목 진척률)
+        <t>▣ 프로그램 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-        </r>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ DRYRUN (세부항목 진척률)
+        <t>▣ DRYRUN (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-        </r>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ AUTORUN (세부항목 진척률)
+        <t>▣ AUTORUN (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-        </r>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 제안서 완료일
+        <t>▣ 제안서 완료일
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD  예: 2026-05-15
 • 허용: 26-5-15, 260515, 2026.5.15 (자동 정규화)
 • 실제 제안서 작성·제출 완료된 날짜 기입
 • 비워두면 미완료 상태
 • 예정일이 아닌 ★실제 완료일★ 만 입력</t>
-        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 설계 완료일 (3D/2D 설계 완료)
+        <t>▣ 설계 완료일 (3D/2D 설계 완료)
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD  예: 2026-06-30
 • 3D/2D 설계가 실제로 완료된 날짜
 • 비워두면 미완료
 • 예정일 아닌 실제 완료일</t>
-        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서 작업 상태
+        <t>▣ 부서 작업 상태
 • 드롭다운 선택:
   미착수 — 작업 시작 안 함
   진행중 — 작업 진행 중
   완료   — 부서 작업 완료
   N/A    — 해당 부서 무관 프로젝트
 • 부서장이 매주 상태 갱신 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 메모 (부서 자유 입력)
+        <t>▣ 메모 (부서 자유 입력)
 • 자유 텍스트 입력
 • 활용:
   - 이슈사항 (예: 자재 결품, 외주 지연)
   - 변경 요청 (예: 사양 변경, 납기 조정)
   - 다른 부서·PM에게 공유할 정보
 • 대시보드 집계에는 미포함</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -1273,18 +1150,18 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" style="55" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="6" customWidth="1" style="55" min="12" max="12"/>
-    <col width="10" customWidth="1" style="55" min="13" max="13"/>
-    <col width="8" customWidth="1" style="55" min="14" max="14"/>
-    <col width="9" customWidth="1" style="55" min="15" max="15"/>
-    <col width="12" customWidth="1" style="55" min="16" max="16"/>
-    <col width="12" customWidth="1" style="55" min="17" max="17"/>
+    <col width="5" customWidth="1" style="55" min="12" max="12"/>
+    <col width="5" customWidth="1" style="55" min="13" max="13"/>
+    <col width="5" customWidth="1" style="55" min="14" max="14"/>
+    <col width="5" customWidth="1" style="55" min="15" max="15"/>
+    <col width="5" customWidth="1" style="55" min="16" max="16"/>
+    <col width="5" customWidth="1" style="55" min="17" max="17"/>
     <col width="10" customWidth="1" style="55" min="18" max="18"/>
     <col width="28" customWidth="1" style="55" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="89" t="inlineStr">
+      <c r="A1" s="94" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 소프트웨어팀 │ 2026</t>
         </is>
@@ -1309,7 +1186,7 @@
       <c r="S1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="90" t="inlineStr">
+      <c r="A2" s="95" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 소프트웨어팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1329,13 +1206,13 @@
       <c r="N2" s="16" t="n"/>
       <c r="O2" s="16" t="n"/>
       <c r="P2" s="17" t="n"/>
-      <c r="Q2" s="91" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:56</t>
-        </is>
-      </c>
-      <c r="R2" s="92" t="n"/>
-      <c r="S2" s="93" t="n"/>
+      <c r="Q2" s="96" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:27</t>
+        </is>
+      </c>
+      <c r="R2" s="16" t="n"/>
+      <c r="S2" s="17" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,17 +1374,20 @@
       </c>
       <c r="M4" s="7" t="inlineStr">
         <is>
-          <t>프로그램</t>
+          <t>프로그
+램</t>
         </is>
       </c>
       <c r="N4" s="7" t="inlineStr">
         <is>
-          <t>DRYRUN</t>
+          <t>DRY
+RUN</t>
         </is>
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>AUTORUN</t>
+          <t>AUT
+ORUN</t>
         </is>
       </c>
       <c r="P4" s="70" t="inlineStr">
@@ -1578,8 +1458,10 @@
         </is>
       </c>
       <c r="J5" s="9" t="n"/>
-      <c r="K5" s="10" t="n">
-        <v>0</v>
+      <c r="K5" s="10" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L5" s="11" t="n"/>
       <c r="M5" s="11" t="n"/>
@@ -1635,8 +1517,10 @@
         </is>
       </c>
       <c r="J6" s="13" t="n"/>
-      <c r="K6" s="14" t="n">
-        <v>0</v>
+      <c r="K6" s="14" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L6" s="15" t="n"/>
       <c r="M6" s="15" t="n"/>
@@ -1692,8 +1576,10 @@
         </is>
       </c>
       <c r="J7" s="9" t="n"/>
-      <c r="K7" s="10" t="n">
-        <v>0</v>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L7" s="11" t="n"/>
       <c r="M7" s="11" t="n"/>
@@ -1749,8 +1635,10 @@
         </is>
       </c>
       <c r="J8" s="13" t="n"/>
-      <c r="K8" s="14" t="n">
-        <v>0</v>
+      <c r="K8" s="14" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L8" s="15" t="n"/>
       <c r="M8" s="15" t="n"/>
@@ -1806,8 +1694,10 @@
         </is>
       </c>
       <c r="J9" s="9" t="n"/>
-      <c r="K9" s="10" t="n">
-        <v>0</v>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L9" s="11" t="n"/>
       <c r="M9" s="11" t="n"/>
@@ -1863,8 +1753,10 @@
         </is>
       </c>
       <c r="J10" s="13" t="n"/>
-      <c r="K10" s="14" t="n">
-        <v>0</v>
+      <c r="K10" s="14" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L10" s="15" t="n"/>
       <c r="M10" s="15" t="n"/>
@@ -1920,8 +1812,10 @@
         </is>
       </c>
       <c r="J11" s="9" t="n"/>
-      <c r="K11" s="10" t="n">
-        <v>0</v>
+      <c r="K11" s="10" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L11" s="11" t="n"/>
       <c r="M11" s="11" t="n"/>
@@ -1977,8 +1871,10 @@
         </is>
       </c>
       <c r="J12" s="13" t="n"/>
-      <c r="K12" s="14" t="n">
-        <v>0</v>
+      <c r="K12" s="14" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15" t="n"/>
@@ -2034,8 +1930,10 @@
         </is>
       </c>
       <c r="J13" s="9" t="n"/>
-      <c r="K13" s="10" t="n">
-        <v>0</v>
+      <c r="K13" s="10" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L13" s="11" t="n"/>
       <c r="M13" s="11" t="n"/>
@@ -2091,8 +1989,10 @@
         </is>
       </c>
       <c r="J14" s="13" t="n"/>
-      <c r="K14" s="14" t="n">
-        <v>0</v>
+      <c r="K14" s="14" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L14" s="15" t="n"/>
       <c r="M14" s="15" t="n"/>
@@ -2148,8 +2048,10 @@
         </is>
       </c>
       <c r="J15" s="9" t="n"/>
-      <c r="K15" s="10" t="n">
-        <v>0</v>
+      <c r="K15" s="10" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L15" s="11" t="n"/>
       <c r="M15" s="11" t="n"/>
@@ -2205,8 +2107,10 @@
         </is>
       </c>
       <c r="J16" s="13" t="n"/>
-      <c r="K16" s="14" t="n">
-        <v>0</v>
+      <c r="K16" s="14" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L16" s="15" t="n"/>
       <c r="M16" s="15" t="n"/>
@@ -2262,8 +2166,10 @@
         </is>
       </c>
       <c r="J17" s="9" t="n"/>
-      <c r="K17" s="10" t="n">
-        <v>0</v>
+      <c r="K17" s="10" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L17" s="11" t="n"/>
       <c r="M17" s="11" t="n"/>
@@ -2319,8 +2225,10 @@
         </is>
       </c>
       <c r="J18" s="13" t="n"/>
-      <c r="K18" s="14" t="n">
-        <v>0</v>
+      <c r="K18" s="14" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L18" s="15" t="n"/>
       <c r="M18" s="15" t="n"/>
@@ -2376,8 +2284,10 @@
         </is>
       </c>
       <c r="J19" s="9" t="n"/>
-      <c r="K19" s="10" t="n">
-        <v>0</v>
+      <c r="K19" s="10" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L19" s="11" t="n"/>
       <c r="M19" s="11" t="n"/>
@@ -2433,8 +2343,10 @@
         </is>
       </c>
       <c r="J20" s="13" t="n"/>
-      <c r="K20" s="14" t="n">
-        <v>0</v>
+      <c r="K20" s="14" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L20" s="15" t="n"/>
       <c r="M20" s="15" t="n"/>
@@ -2490,8 +2402,10 @@
         </is>
       </c>
       <c r="J21" s="9" t="n"/>
-      <c r="K21" s="10" t="n">
-        <v>0</v>
+      <c r="K21" s="10" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L21" s="11" t="n"/>
       <c r="M21" s="11" t="n"/>
@@ -2547,8 +2461,10 @@
         </is>
       </c>
       <c r="J22" s="13" t="n"/>
-      <c r="K22" s="14" t="n">
-        <v>0</v>
+      <c r="K22" s="14" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L22" s="15" t="n"/>
       <c r="M22" s="15" t="n"/>
@@ -2604,8 +2520,10 @@
         </is>
       </c>
       <c r="J23" s="9" t="n"/>
-      <c r="K23" s="10" t="n">
-        <v>0</v>
+      <c r="K23" s="10" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L23" s="11" t="n"/>
       <c r="M23" s="11" t="n"/>
@@ -2661,8 +2579,10 @@
         </is>
       </c>
       <c r="J24" s="13" t="n"/>
-      <c r="K24" s="14" t="n">
-        <v>0</v>
+      <c r="K24" s="14" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L24" s="15" t="n"/>
       <c r="M24" s="15" t="n"/>
@@ -2718,8 +2638,10 @@
         </is>
       </c>
       <c r="J25" s="9" t="n"/>
-      <c r="K25" s="10" t="n">
-        <v>0</v>
+      <c r="K25" s="10" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L25" s="11" t="n"/>
       <c r="M25" s="11" t="n"/>
@@ -2775,8 +2697,10 @@
         </is>
       </c>
       <c r="J26" s="13" t="n"/>
-      <c r="K26" s="14" t="n">
-        <v>0</v>
+      <c r="K26" s="14" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L26" s="15" t="n"/>
       <c r="M26" s="15" t="n"/>
@@ -2832,8 +2756,10 @@
         </is>
       </c>
       <c r="J27" s="9" t="n"/>
-      <c r="K27" s="10" t="n">
-        <v>0</v>
+      <c r="K27" s="10" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L27" s="11" t="n"/>
       <c r="M27" s="11" t="n"/>

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_소프트웨어팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_소프트웨어팀_입력_2026.xlsx
@@ -237,7 +237,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -516,6 +516,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -609,15 +618,30 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -631,46 +655,86 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 모델 (장비 모델명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ PO유형 (발주 성격)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -681,11 +745,19 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
+        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 영업단계 (Sales Pipeline)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -700,31 +772,55 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
+        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 진행상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
+        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 담당자
 • 부서 내 실제 담당자 이름 입력
   예: 정민규, 한재운, 이찬
 • 입력 시: PMS에도 자동 반영
 • 빈 칸: 부서 참여 확정, 담당자 미정</t>
+        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 진척률 (%) — 본인 부서 작업
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 진척률 (%) — 본인 부서 작업
 • 자동 계산 (수정 불가, sync 시 갱신)
 • 시작일·완료일 입력 기반:
     0%  = 미착수    (시작일·완료일 모두 빈 칸)
@@ -733,11 +829,19 @@
 • ★ 이 값은 '이 부서'만의 진척률입니다.
 • 프로젝트 전체 진척률은 PMS 1_프로젝트등록
   '진척률(%)' 컬럼에서 확인 (= 완료부서/참여부서)</t>
+        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 검토 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 검토 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -749,11 +853,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 프로그램 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 프로그램 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -765,11 +877,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>▣ DRYRUN (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ DRYRUN (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -781,11 +901,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>▣ AUTORUN (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ AUTORUN (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -797,49 +925,82 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 제안서 완료일
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 제안서 완료일
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD  예: 2026-05-15
 • 허용: 26-5-15, 260515, 2026.5.15 (자동 정규화)
 • 실제 제안서 작성·제출 완료된 날짜 기입
 • 비워두면 미완료 상태
 • 예정일이 아닌 ★실제 완료일★ 만 입력</t>
+        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 설계 완료일 (3D/2D 설계 완료)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 설계 완료일 (3D/2D 설계 완료)
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD  예: 2026-06-30
 • 3D/2D 설계가 실제로 완료된 날짜
 • 비워두면 미완료
 • 예정일 아닌 실제 완료일</t>
+        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 작업 상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 작업 상태
 • 드롭다운 선택:
   미착수 — 작업 시작 안 함
   진행중 — 작업 진행 중
   완료   — 부서 작업 완료
   N/A    — 해당 부서 무관 프로젝트
 • 부서장이 매주 상태 갱신 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 메모 (부서 자유 입력)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 메모 (부서 자유 입력)
 • 자유 텍스트 입력
 • 활용:
   - 이슈사항 (예: 자재 결품, 외주 지연)
   - 변경 요청 (예: 사양 변경, 납기 조정)
   - 다른 부서·PM에게 공유할 정보
 • 대시보드 집계에는 미포함</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -1150,18 +1311,18 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" style="55" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="5" customWidth="1" style="55" min="12" max="12"/>
-    <col width="5" customWidth="1" style="55" min="13" max="13"/>
-    <col width="5" customWidth="1" style="55" min="14" max="14"/>
-    <col width="5" customWidth="1" style="55" min="15" max="15"/>
-    <col width="5" customWidth="1" style="55" min="16" max="16"/>
-    <col width="5" customWidth="1" style="55" min="17" max="17"/>
+    <col width="7" customWidth="1" style="55" min="12" max="12"/>
+    <col width="7" customWidth="1" style="55" min="13" max="13"/>
+    <col width="7" customWidth="1" style="55" min="14" max="14"/>
+    <col width="7" customWidth="1" style="55" min="15" max="15"/>
+    <col width="7" customWidth="1" style="55" min="16" max="16"/>
+    <col width="7" customWidth="1" style="55" min="17" max="17"/>
     <col width="10" customWidth="1" style="55" min="18" max="18"/>
     <col width="28" customWidth="1" style="55" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="94" t="inlineStr">
+      <c r="A1" s="97" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 소프트웨어팀 │ 2026</t>
         </is>
@@ -1186,7 +1347,7 @@
       <c r="S1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="95" t="inlineStr">
+      <c r="A2" s="98" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 소프트웨어팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1206,9 +1367,9 @@
       <c r="N2" s="16" t="n"/>
       <c r="O2" s="16" t="n"/>
       <c r="P2" s="17" t="n"/>
-      <c r="Q2" s="96" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:27</t>
+      <c r="Q2" s="99" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:39</t>
         </is>
       </c>
       <c r="R2" s="16" t="n"/>
@@ -1374,8 +1535,8 @@
       </c>
       <c r="M4" s="7" t="inlineStr">
         <is>
-          <t>프로그
-램</t>
+          <t>프로
+그램</t>
         </is>
       </c>
       <c r="N4" s="7" t="inlineStr">
@@ -1386,8 +1547,8 @@
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>AUT
-ORUN</t>
+          <t>AUTO
+RUN</t>
         </is>
       </c>
       <c r="P4" s="70" t="inlineStr">

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_소프트웨어팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_소프트웨어팀_입력_2026.xlsx
@@ -237,7 +237,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -516,6 +516,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -618,30 +627,15 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ NO (일련번호)
+        <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
-        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 관리코드 (프로젝트 고유 번호)
+        <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -655,86 +649,46 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주번호
+        <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
-        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 고객사 (거래처명)
+        <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 모델 (장비 모델명)
+        <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
-        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
-        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ PO유형 (발주 성격)
+        <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -745,19 +699,11 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
-        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 영업단계 (Sales Pipeline)
+        <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -772,55 +718,31 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
-        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 진행상태
+        <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
-        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서 담당자
+        <t>▣ 부서 담당자
 • 부서 내 실제 담당자 이름 입력
   예: 정민규, 한재운, 이찬
 • 입력 시: PMS에도 자동 반영
 • 빈 칸: 부서 참여 확정, 담당자 미정</t>
-        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서 진척률 (%) — 본인 부서 작업
+        <t>▣ 부서 진척률 (%) — 본인 부서 작업
 • 자동 계산 (수정 불가, sync 시 갱신)
 • 시작일·완료일 입력 기반:
     0%  = 미착수    (시작일·완료일 모두 빈 칸)
@@ -829,19 +751,11 @@
 • ★ 이 값은 '이 부서'만의 진척률입니다.
 • 프로젝트 전체 진척률은 PMS 1_프로젝트등록
   '진척률(%)' 컬럼에서 확인 (= 완료부서/참여부서)</t>
-        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 검토 (세부항목 진척률)
+        <t>▣ 검토 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -853,19 +767,11 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 프로그램 (세부항목 진척률)
+        <t>▣ 프로그램 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -877,19 +783,11 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ DRYRUN (세부항목 진척률)
+        <t>▣ DRYRUN (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -901,19 +799,11 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ AUTORUN (세부항목 진척률)
+        <t>▣ AUTORUN (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -925,82 +815,49 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 제안서 완료일
+        <t>▣ 제안서 완료일
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD  예: 2026-05-15
 • 허용: 26-5-15, 260515, 2026.5.15 (자동 정규화)
 • 실제 제안서 작성·제출 완료된 날짜 기입
 • 비워두면 미완료 상태
 • 예정일이 아닌 ★실제 완료일★ 만 입력</t>
-        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 설계 완료일 (3D/2D 설계 완료)
+        <t>▣ 설계 완료일 (3D/2D 설계 완료)
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD  예: 2026-06-30
 • 3D/2D 설계가 실제로 완료된 날짜
 • 비워두면 미완료
 • 예정일 아닌 실제 완료일</t>
-        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서 작업 상태
+        <t>▣ 부서 작업 상태
 • 드롭다운 선택:
   미착수 — 작업 시작 안 함
   진행중 — 작업 진행 중
   완료   — 부서 작업 완료
   N/A    — 해당 부서 무관 프로젝트
 • 부서장이 매주 상태 갱신 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 메모 (부서 자유 입력)
+        <t>▣ 메모 (부서 자유 입력)
 • 자유 텍스트 입력
 • 활용:
   - 이슈사항 (예: 자재 결품, 외주 지연)
   - 변경 요청 (예: 사양 변경, 납기 조정)
   - 다른 부서·PM에게 공유할 정보
 • 대시보드 집계에는 미포함</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -1322,7 +1179,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="97" t="inlineStr">
+      <c r="A1" s="100" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 소프트웨어팀 │ 2026</t>
         </is>
@@ -1347,7 +1204,7 @@
       <c r="S1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="98" t="inlineStr">
+      <c r="A2" s="101" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 소프트웨어팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1367,9 +1224,9 @@
       <c r="N2" s="16" t="n"/>
       <c r="O2" s="16" t="n"/>
       <c r="P2" s="17" t="n"/>
-      <c r="Q2" s="99" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:39</t>
+      <c r="Q2" s="102" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:47</t>
         </is>
       </c>
       <c r="R2" s="16" t="n"/>

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_소프트웨어팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_소프트웨어팀_입력_2026.xlsx
@@ -237,7 +237,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -516,6 +516,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -627,15 +636,30 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -649,46 +673,86 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 모델 (장비 모델명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ PO유형 (발주 성격)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -699,11 +763,19 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
+        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 영업단계 (Sales Pipeline)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -718,31 +790,55 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
+        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 진행상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
+        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 담당자
 • 부서 내 실제 담당자 이름 입력
   예: 정민규, 한재운, 이찬
 • 입력 시: PMS에도 자동 반영
 • 빈 칸: 부서 참여 확정, 담당자 미정</t>
+        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 진척률 (%) — 본인 부서 작업
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 진척률 (%) — 본인 부서 작업
 • 자동 계산 (수정 불가, sync 시 갱신)
 • 시작일·완료일 입력 기반:
     0%  = 미착수    (시작일·완료일 모두 빈 칸)
@@ -751,11 +847,19 @@
 • ★ 이 값은 '이 부서'만의 진척률입니다.
 • 프로젝트 전체 진척률은 PMS 1_프로젝트등록
   '진척률(%)' 컬럼에서 확인 (= 완료부서/참여부서)</t>
+        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 검토 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 검토 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -767,11 +871,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 프로그램 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 프로그램 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -783,11 +895,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>▣ DRYRUN (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ DRYRUN (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -799,11 +919,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>▣ AUTORUN (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ AUTORUN (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -815,49 +943,82 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 제안서 완료일
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 제안서 완료일
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD  예: 2026-05-15
 • 허용: 26-5-15, 260515, 2026.5.15 (자동 정규화)
 • 실제 제안서 작성·제출 완료된 날짜 기입
 • 비워두면 미완료 상태
 • 예정일이 아닌 ★실제 완료일★ 만 입력</t>
+        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 설계 완료일 (3D/2D 설계 완료)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 설계 완료일 (3D/2D 설계 완료)
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD  예: 2026-06-30
 • 3D/2D 설계가 실제로 완료된 날짜
 • 비워두면 미완료
 • 예정일 아닌 실제 완료일</t>
+        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 작업 상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 작업 상태
 • 드롭다운 선택:
   미착수 — 작업 시작 안 함
   진행중 — 작업 진행 중
   완료   — 부서 작업 완료
   N/A    — 해당 부서 무관 프로젝트
 • 부서장이 매주 상태 갱신 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 메모 (부서 자유 입력)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 메모 (부서 자유 입력)
 • 자유 텍스트 입력
 • 활용:
   - 이슈사항 (예: 자재 결품, 외주 지연)
   - 변경 요청 (예: 사양 변경, 납기 조정)
   - 다른 부서·PM에게 공유할 정보
 • 대시보드 집계에는 미포함</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -1179,7 +1340,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="100" t="inlineStr">
+      <c r="A1" s="103" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 소프트웨어팀 │ 2026</t>
         </is>
@@ -1204,7 +1365,7 @@
       <c r="S1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="101" t="inlineStr">
+      <c r="A2" s="104" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 소프트웨어팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1224,9 +1385,9 @@
       <c r="N2" s="16" t="n"/>
       <c r="O2" s="16" t="n"/>
       <c r="P2" s="17" t="n"/>
-      <c r="Q2" s="102" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:47</t>
+      <c r="Q2" s="105" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 14:00</t>
         </is>
       </c>
       <c r="R2" s="16" t="n"/>

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_소프트웨어팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_소프트웨어팀_입력_2026.xlsx
@@ -237,7 +237,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -516,6 +516,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -883,6 +901,28 @@
             <family val="3"/>
             <charset val="129"/>
           </rPr>
+          <t>▣ 검토 — 완료 예정일
+★ 날짜 입력 (% 아님 ⚠️)
+• 형식: YYYY-MM-DD  예: 2026-07-15
+• 검토 작업의 ★완료 예정일★ 기입
+📋 운영:
+  ▸ 좌측 셀 = 진척률(%)
+  ▸ 이 셀  = 검토 완료 목표일
+  ▸ 진척률과 비교 → 일정 대비 진행도 추적
+  ▸ 예: 7/15까지 100% 목표인데 7/10 현재 50% → 일정 빠름
+• 비워두면: 일정 미정 또는 해당없음</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
           <t>▣ 프로그램 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
@@ -898,7 +938,29 @@
         </r>
       </text>
     </comment>
-    <comment ref="N4" authorId="0" shapeId="0">
+    <comment ref="O4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 프로그램 — 완료 예정일
+★ 날짜 입력 (% 아님 ⚠️)
+• 형식: YYYY-MM-DD  예: 2026-07-15
+• 프로그램 작업의 ★완료 예정일★ 기입
+📋 운영:
+  ▸ 좌측 셀 = 진척률(%)
+  ▸ 이 셀  = 프로그램 완료 목표일
+  ▸ 진척률과 비교 → 일정 대비 진행도 추적
+  ▸ 예: 7/15까지 100% 목표인데 7/10 현재 50% → 일정 빠름
+• 비워두면: 일정 미정 또는 해당없음</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -922,7 +984,29 @@
         </r>
       </text>
     </comment>
-    <comment ref="O4" authorId="0" shapeId="0">
+    <comment ref="Q4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ DRYRUN — 완료 예정일
+★ 날짜 입력 (% 아님 ⚠️)
+• 형식: YYYY-MM-DD  예: 2026-07-15
+• DRYRUN 작업의 ★완료 예정일★ 기입
+📋 운영:
+  ▸ 좌측 셀 = 진척률(%)
+  ▸ 이 셀  = DRYRUN 완료 목표일
+  ▸ 진척률과 비교 → 일정 대비 진행도 추적
+  ▸ 예: 7/15까지 100% 목표인데 7/10 현재 50% → 일정 빠름
+• 비워두면: 일정 미정 또는 해당없음</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="R4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -946,7 +1030,29 @@
         </r>
       </text>
     </comment>
-    <comment ref="P4" authorId="0" shapeId="0">
+    <comment ref="S4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ AUTORUN — 완료 예정일
+★ 날짜 입력 (% 아님 ⚠️)
+• 형식: YYYY-MM-DD  예: 2026-07-15
+• AUTORUN 작업의 ★완료 예정일★ 기입
+📋 운영:
+  ▸ 좌측 셀 = 진척률(%)
+  ▸ 이 셀  = AUTORUN 완료 목표일
+  ▸ 진척률과 비교 → 일정 대비 진행도 추적
+  ▸ 예: 7/15까지 100% 목표인데 7/10 현재 50% → 일정 빠름
+• 비워두면: 일정 미정 또는 해당없음</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -965,7 +1071,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q4" authorId="0" shapeId="0">
+    <comment ref="U4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -983,7 +1089,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R4" authorId="0" shapeId="0">
+    <comment ref="V4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1002,7 +1108,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S4" authorId="0" shapeId="0">
+    <comment ref="W4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1315,7 +1421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S57"/>
+  <dimension ref="A1:W57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1335,12 +1441,16 @@
     <col width="7" customWidth="1" style="55" min="15" max="15"/>
     <col width="7" customWidth="1" style="55" min="16" max="16"/>
     <col width="7" customWidth="1" style="55" min="17" max="17"/>
-    <col width="10" customWidth="1" style="55" min="18" max="18"/>
-    <col width="28" customWidth="1" style="55" min="19" max="19"/>
+    <col width="7" customWidth="1" style="55" min="18" max="18"/>
+    <col width="7" customWidth="1" style="55" min="19" max="19"/>
+    <col width="7" customWidth="1" style="55" min="20" max="20"/>
+    <col width="7" customWidth="1" style="55" min="21" max="21"/>
+    <col width="10" customWidth="1" style="55" min="22" max="22"/>
+    <col width="28" customWidth="1" style="55" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="103" t="inlineStr">
+      <c r="A1" s="109" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 소프트웨어팀 │ 2026</t>
         </is>
@@ -1362,10 +1472,14 @@
       <c r="P1" s="16" t="n"/>
       <c r="Q1" s="16" t="n"/>
       <c r="R1" s="16" t="n"/>
-      <c r="S1" s="17" t="n"/>
+      <c r="S1" s="16" t="n"/>
+      <c r="T1" s="16" t="n"/>
+      <c r="U1" s="16" t="n"/>
+      <c r="V1" s="16" t="n"/>
+      <c r="W1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="104" t="inlineStr">
+      <c r="A2" s="110" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 소프트웨어팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1384,14 +1498,18 @@
       <c r="M2" s="16" t="n"/>
       <c r="N2" s="16" t="n"/>
       <c r="O2" s="16" t="n"/>
-      <c r="P2" s="17" t="n"/>
-      <c r="Q2" s="105" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 14:00</t>
-        </is>
-      </c>
+      <c r="P2" s="16" t="n"/>
+      <c r="Q2" s="16" t="n"/>
       <c r="R2" s="16" t="n"/>
-      <c r="S2" s="17" t="n"/>
+      <c r="S2" s="16" t="n"/>
+      <c r="T2" s="17" t="n"/>
+      <c r="U2" s="111" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 14:35</t>
+        </is>
+      </c>
+      <c r="V2" s="16" t="n"/>
+      <c r="W2" s="17" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -1454,37 +1572,57 @@
           <t>✏입력</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>PO후입력</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>✏입력</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>PO후입력</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>✏입력</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>PO후입력</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
         <is>
           <t>✏입력</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="S3" s="4" t="inlineStr">
         <is>
           <t>PO후입력</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="T3" s="4" t="inlineStr">
         <is>
           <t>PO후입력</t>
         </is>
       </c>
-      <c r="R3" s="3" t="inlineStr">
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t>PO후입력</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
         <is>
           <t>✏선택▼</t>
         </is>
       </c>
-      <c r="S3" s="4" t="inlineStr">
+      <c r="W3" s="4" t="inlineStr">
         <is>
           <t>✏메모</t>
         </is>
@@ -1551,42 +1689,62 @@
           <t>검토</t>
         </is>
       </c>
-      <c r="M4" s="7" t="inlineStr">
+      <c r="M4" s="70" t="inlineStr">
+        <is>
+          <t>예정일</t>
+        </is>
+      </c>
+      <c r="N4" s="7" t="inlineStr">
         <is>
           <t>프로
 그램</t>
         </is>
       </c>
-      <c r="N4" s="7" t="inlineStr">
+      <c r="O4" s="70" t="inlineStr">
+        <is>
+          <t>예정일</t>
+        </is>
+      </c>
+      <c r="P4" s="7" t="inlineStr">
         <is>
           <t>DRY
 RUN</t>
         </is>
       </c>
-      <c r="O4" s="7" t="inlineStr">
+      <c r="Q4" s="70" t="inlineStr">
+        <is>
+          <t>예정일</t>
+        </is>
+      </c>
+      <c r="R4" s="7" t="inlineStr">
         <is>
           <t>AUTO
 RUN</t>
         </is>
       </c>
-      <c r="P4" s="70" t="inlineStr">
+      <c r="S4" s="70" t="inlineStr">
+        <is>
+          <t>예정일</t>
+        </is>
+      </c>
+      <c r="T4" s="70" t="inlineStr">
         <is>
           <t>제안서
 완료일</t>
         </is>
       </c>
-      <c r="Q4" s="70" t="inlineStr">
+      <c r="U4" s="70" t="inlineStr">
         <is>
           <t>설계
 완료일</t>
         </is>
       </c>
-      <c r="R4" s="7" t="inlineStr">
+      <c r="V4" s="7" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="S4" s="7" t="inlineStr">
+      <c r="W4" s="7" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
@@ -1649,7 +1807,11 @@
       <c r="P5" s="9" t="n"/>
       <c r="Q5" s="9" t="n"/>
       <c r="R5" s="9" t="n"/>
-      <c r="S5" s="22" t="n"/>
+      <c r="S5" s="9" t="n"/>
+      <c r="T5" s="9" t="n"/>
+      <c r="U5" s="9" t="n"/>
+      <c r="V5" s="9" t="n"/>
+      <c r="W5" s="22" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="12" t="n">
@@ -1708,7 +1870,11 @@
       <c r="P6" s="13" t="n"/>
       <c r="Q6" s="13" t="n"/>
       <c r="R6" s="13" t="n"/>
-      <c r="S6" s="24" t="n"/>
+      <c r="S6" s="13" t="n"/>
+      <c r="T6" s="13" t="n"/>
+      <c r="U6" s="13" t="n"/>
+      <c r="V6" s="13" t="n"/>
+      <c r="W6" s="24" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="8" t="n">
@@ -1767,7 +1933,11 @@
       <c r="P7" s="9" t="n"/>
       <c r="Q7" s="9" t="n"/>
       <c r="R7" s="9" t="n"/>
-      <c r="S7" s="22" t="n"/>
+      <c r="S7" s="9" t="n"/>
+      <c r="T7" s="9" t="n"/>
+      <c r="U7" s="9" t="n"/>
+      <c r="V7" s="9" t="n"/>
+      <c r="W7" s="22" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="12" t="n">
@@ -1826,7 +1996,11 @@
       <c r="P8" s="13" t="n"/>
       <c r="Q8" s="13" t="n"/>
       <c r="R8" s="13" t="n"/>
-      <c r="S8" s="24" t="n"/>
+      <c r="S8" s="13" t="n"/>
+      <c r="T8" s="13" t="n"/>
+      <c r="U8" s="13" t="n"/>
+      <c r="V8" s="13" t="n"/>
+      <c r="W8" s="24" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="8" t="n">
@@ -1885,7 +2059,11 @@
       <c r="P9" s="9" t="n"/>
       <c r="Q9" s="9" t="n"/>
       <c r="R9" s="9" t="n"/>
-      <c r="S9" s="22" t="n"/>
+      <c r="S9" s="9" t="n"/>
+      <c r="T9" s="9" t="n"/>
+      <c r="U9" s="9" t="n"/>
+      <c r="V9" s="9" t="n"/>
+      <c r="W9" s="22" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="12" t="n">
@@ -1944,7 +2122,11 @@
       <c r="P10" s="13" t="n"/>
       <c r="Q10" s="13" t="n"/>
       <c r="R10" s="13" t="n"/>
-      <c r="S10" s="24" t="n"/>
+      <c r="S10" s="13" t="n"/>
+      <c r="T10" s="13" t="n"/>
+      <c r="U10" s="13" t="n"/>
+      <c r="V10" s="13" t="n"/>
+      <c r="W10" s="24" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="8" t="n">
@@ -2003,7 +2185,11 @@
       <c r="P11" s="9" t="n"/>
       <c r="Q11" s="9" t="n"/>
       <c r="R11" s="9" t="n"/>
-      <c r="S11" s="22" t="n"/>
+      <c r="S11" s="9" t="n"/>
+      <c r="T11" s="9" t="n"/>
+      <c r="U11" s="9" t="n"/>
+      <c r="V11" s="9" t="n"/>
+      <c r="W11" s="22" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="12" t="n">
@@ -2062,7 +2248,11 @@
       <c r="P12" s="13" t="n"/>
       <c r="Q12" s="13" t="n"/>
       <c r="R12" s="13" t="n"/>
-      <c r="S12" s="24" t="n"/>
+      <c r="S12" s="13" t="n"/>
+      <c r="T12" s="13" t="n"/>
+      <c r="U12" s="13" t="n"/>
+      <c r="V12" s="13" t="n"/>
+      <c r="W12" s="24" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="8" t="n">
@@ -2121,7 +2311,11 @@
       <c r="P13" s="9" t="n"/>
       <c r="Q13" s="9" t="n"/>
       <c r="R13" s="9" t="n"/>
-      <c r="S13" s="22" t="n"/>
+      <c r="S13" s="9" t="n"/>
+      <c r="T13" s="9" t="n"/>
+      <c r="U13" s="9" t="n"/>
+      <c r="V13" s="9" t="n"/>
+      <c r="W13" s="22" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="12" t="n">
@@ -2180,7 +2374,11 @@
       <c r="P14" s="13" t="n"/>
       <c r="Q14" s="13" t="n"/>
       <c r="R14" s="13" t="n"/>
-      <c r="S14" s="24" t="n"/>
+      <c r="S14" s="13" t="n"/>
+      <c r="T14" s="13" t="n"/>
+      <c r="U14" s="13" t="n"/>
+      <c r="V14" s="13" t="n"/>
+      <c r="W14" s="24" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="8" t="n">
@@ -2239,7 +2437,11 @@
       <c r="P15" s="9" t="n"/>
       <c r="Q15" s="9" t="n"/>
       <c r="R15" s="9" t="n"/>
-      <c r="S15" s="22" t="n"/>
+      <c r="S15" s="9" t="n"/>
+      <c r="T15" s="9" t="n"/>
+      <c r="U15" s="9" t="n"/>
+      <c r="V15" s="9" t="n"/>
+      <c r="W15" s="22" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="12" t="n">
@@ -2298,7 +2500,11 @@
       <c r="P16" s="13" t="n"/>
       <c r="Q16" s="13" t="n"/>
       <c r="R16" s="13" t="n"/>
-      <c r="S16" s="24" t="n"/>
+      <c r="S16" s="13" t="n"/>
+      <c r="T16" s="13" t="n"/>
+      <c r="U16" s="13" t="n"/>
+      <c r="V16" s="13" t="n"/>
+      <c r="W16" s="24" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="8" t="n">
@@ -2357,7 +2563,11 @@
       <c r="P17" s="9" t="n"/>
       <c r="Q17" s="9" t="n"/>
       <c r="R17" s="9" t="n"/>
-      <c r="S17" s="22" t="n"/>
+      <c r="S17" s="9" t="n"/>
+      <c r="T17" s="9" t="n"/>
+      <c r="U17" s="9" t="n"/>
+      <c r="V17" s="9" t="n"/>
+      <c r="W17" s="22" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="12" t="n">
@@ -2416,7 +2626,11 @@
       <c r="P18" s="13" t="n"/>
       <c r="Q18" s="13" t="n"/>
       <c r="R18" s="13" t="n"/>
-      <c r="S18" s="24" t="n"/>
+      <c r="S18" s="13" t="n"/>
+      <c r="T18" s="13" t="n"/>
+      <c r="U18" s="13" t="n"/>
+      <c r="V18" s="13" t="n"/>
+      <c r="W18" s="24" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="8" t="n">
@@ -2475,7 +2689,11 @@
       <c r="P19" s="9" t="n"/>
       <c r="Q19" s="9" t="n"/>
       <c r="R19" s="9" t="n"/>
-      <c r="S19" s="22" t="n"/>
+      <c r="S19" s="9" t="n"/>
+      <c r="T19" s="9" t="n"/>
+      <c r="U19" s="9" t="n"/>
+      <c r="V19" s="9" t="n"/>
+      <c r="W19" s="22" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="12" t="n">
@@ -2534,7 +2752,11 @@
       <c r="P20" s="13" t="n"/>
       <c r="Q20" s="13" t="n"/>
       <c r="R20" s="13" t="n"/>
-      <c r="S20" s="24" t="n"/>
+      <c r="S20" s="13" t="n"/>
+      <c r="T20" s="13" t="n"/>
+      <c r="U20" s="13" t="n"/>
+      <c r="V20" s="13" t="n"/>
+      <c r="W20" s="24" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="8" t="n">
@@ -2593,7 +2815,11 @@
       <c r="P21" s="9" t="n"/>
       <c r="Q21" s="9" t="n"/>
       <c r="R21" s="9" t="n"/>
-      <c r="S21" s="22" t="n"/>
+      <c r="S21" s="9" t="n"/>
+      <c r="T21" s="9" t="n"/>
+      <c r="U21" s="9" t="n"/>
+      <c r="V21" s="9" t="n"/>
+      <c r="W21" s="22" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="12" t="n">
@@ -2652,7 +2878,11 @@
       <c r="P22" s="13" t="n"/>
       <c r="Q22" s="13" t="n"/>
       <c r="R22" s="13" t="n"/>
-      <c r="S22" s="24" t="n"/>
+      <c r="S22" s="13" t="n"/>
+      <c r="T22" s="13" t="n"/>
+      <c r="U22" s="13" t="n"/>
+      <c r="V22" s="13" t="n"/>
+      <c r="W22" s="24" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="8" t="n">
@@ -2711,7 +2941,11 @@
       <c r="P23" s="9" t="n"/>
       <c r="Q23" s="9" t="n"/>
       <c r="R23" s="9" t="n"/>
-      <c r="S23" s="22" t="n"/>
+      <c r="S23" s="9" t="n"/>
+      <c r="T23" s="9" t="n"/>
+      <c r="U23" s="9" t="n"/>
+      <c r="V23" s="9" t="n"/>
+      <c r="W23" s="22" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="12" t="n">
@@ -2770,7 +3004,11 @@
       <c r="P24" s="13" t="n"/>
       <c r="Q24" s="13" t="n"/>
       <c r="R24" s="13" t="n"/>
-      <c r="S24" s="24" t="n"/>
+      <c r="S24" s="13" t="n"/>
+      <c r="T24" s="13" t="n"/>
+      <c r="U24" s="13" t="n"/>
+      <c r="V24" s="13" t="n"/>
+      <c r="W24" s="24" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="8" t="n">
@@ -2829,7 +3067,11 @@
       <c r="P25" s="9" t="n"/>
       <c r="Q25" s="9" t="n"/>
       <c r="R25" s="9" t="n"/>
-      <c r="S25" s="22" t="n"/>
+      <c r="S25" s="9" t="n"/>
+      <c r="T25" s="9" t="n"/>
+      <c r="U25" s="9" t="n"/>
+      <c r="V25" s="9" t="n"/>
+      <c r="W25" s="22" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="12" t="n">
@@ -2888,7 +3130,11 @@
       <c r="P26" s="13" t="n"/>
       <c r="Q26" s="13" t="n"/>
       <c r="R26" s="13" t="n"/>
-      <c r="S26" s="24" t="n"/>
+      <c r="S26" s="13" t="n"/>
+      <c r="T26" s="13" t="n"/>
+      <c r="U26" s="13" t="n"/>
+      <c r="V26" s="13" t="n"/>
+      <c r="W26" s="24" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="8" t="n">
@@ -2947,7 +3193,11 @@
       <c r="P27" s="9" t="n"/>
       <c r="Q27" s="9" t="n"/>
       <c r="R27" s="9" t="n"/>
-      <c r="S27" s="22" t="n"/>
+      <c r="S27" s="9" t="n"/>
+      <c r="T27" s="9" t="n"/>
+      <c r="U27" s="9" t="n"/>
+      <c r="V27" s="9" t="n"/>
+      <c r="W27" s="22" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="12" t="n"/>
@@ -2968,7 +3218,11 @@
       <c r="P28" s="13" t="n"/>
       <c r="Q28" s="13" t="n"/>
       <c r="R28" s="13" t="n"/>
-      <c r="S28" s="24" t="n"/>
+      <c r="S28" s="13" t="n"/>
+      <c r="T28" s="13" t="n"/>
+      <c r="U28" s="13" t="n"/>
+      <c r="V28" s="13" t="n"/>
+      <c r="W28" s="24" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="8" t="n"/>
@@ -2989,7 +3243,11 @@
       <c r="P29" s="9" t="n"/>
       <c r="Q29" s="9" t="n"/>
       <c r="R29" s="9" t="n"/>
-      <c r="S29" s="22" t="n"/>
+      <c r="S29" s="9" t="n"/>
+      <c r="T29" s="9" t="n"/>
+      <c r="U29" s="9" t="n"/>
+      <c r="V29" s="9" t="n"/>
+      <c r="W29" s="22" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="12" t="n"/>
@@ -3010,7 +3268,11 @@
       <c r="P30" s="13" t="n"/>
       <c r="Q30" s="13" t="n"/>
       <c r="R30" s="13" t="n"/>
-      <c r="S30" s="24" t="n"/>
+      <c r="S30" s="13" t="n"/>
+      <c r="T30" s="13" t="n"/>
+      <c r="U30" s="13" t="n"/>
+      <c r="V30" s="13" t="n"/>
+      <c r="W30" s="24" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="8" t="n"/>
@@ -3031,7 +3293,11 @@
       <c r="P31" s="9" t="n"/>
       <c r="Q31" s="9" t="n"/>
       <c r="R31" s="9" t="n"/>
-      <c r="S31" s="22" t="n"/>
+      <c r="S31" s="9" t="n"/>
+      <c r="T31" s="9" t="n"/>
+      <c r="U31" s="9" t="n"/>
+      <c r="V31" s="9" t="n"/>
+      <c r="W31" s="22" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="12" t="n"/>
@@ -3052,7 +3318,11 @@
       <c r="P32" s="13" t="n"/>
       <c r="Q32" s="13" t="n"/>
       <c r="R32" s="13" t="n"/>
-      <c r="S32" s="24" t="n"/>
+      <c r="S32" s="13" t="n"/>
+      <c r="T32" s="13" t="n"/>
+      <c r="U32" s="13" t="n"/>
+      <c r="V32" s="13" t="n"/>
+      <c r="W32" s="24" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="8" t="n"/>
@@ -3073,7 +3343,11 @@
       <c r="P33" s="9" t="n"/>
       <c r="Q33" s="9" t="n"/>
       <c r="R33" s="9" t="n"/>
-      <c r="S33" s="22" t="n"/>
+      <c r="S33" s="9" t="n"/>
+      <c r="T33" s="9" t="n"/>
+      <c r="U33" s="9" t="n"/>
+      <c r="V33" s="9" t="n"/>
+      <c r="W33" s="22" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="12" t="n"/>
@@ -3094,7 +3368,11 @@
       <c r="P34" s="13" t="n"/>
       <c r="Q34" s="13" t="n"/>
       <c r="R34" s="13" t="n"/>
-      <c r="S34" s="24" t="n"/>
+      <c r="S34" s="13" t="n"/>
+      <c r="T34" s="13" t="n"/>
+      <c r="U34" s="13" t="n"/>
+      <c r="V34" s="13" t="n"/>
+      <c r="W34" s="24" t="n"/>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="8" t="n"/>
@@ -3115,7 +3393,11 @@
       <c r="P35" s="9" t="n"/>
       <c r="Q35" s="9" t="n"/>
       <c r="R35" s="9" t="n"/>
-      <c r="S35" s="22" t="n"/>
+      <c r="S35" s="9" t="n"/>
+      <c r="T35" s="9" t="n"/>
+      <c r="U35" s="9" t="n"/>
+      <c r="V35" s="9" t="n"/>
+      <c r="W35" s="22" t="n"/>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="12" t="n"/>
@@ -3136,7 +3418,11 @@
       <c r="P36" s="13" t="n"/>
       <c r="Q36" s="13" t="n"/>
       <c r="R36" s="13" t="n"/>
-      <c r="S36" s="24" t="n"/>
+      <c r="S36" s="13" t="n"/>
+      <c r="T36" s="13" t="n"/>
+      <c r="U36" s="13" t="n"/>
+      <c r="V36" s="13" t="n"/>
+      <c r="W36" s="24" t="n"/>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="8" t="n"/>
@@ -3157,7 +3443,11 @@
       <c r="P37" s="9" t="n"/>
       <c r="Q37" s="9" t="n"/>
       <c r="R37" s="9" t="n"/>
-      <c r="S37" s="22" t="n"/>
+      <c r="S37" s="9" t="n"/>
+      <c r="T37" s="9" t="n"/>
+      <c r="U37" s="9" t="n"/>
+      <c r="V37" s="9" t="n"/>
+      <c r="W37" s="22" t="n"/>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="12" t="n"/>
@@ -3178,7 +3468,11 @@
       <c r="P38" s="13" t="n"/>
       <c r="Q38" s="13" t="n"/>
       <c r="R38" s="13" t="n"/>
-      <c r="S38" s="24" t="n"/>
+      <c r="S38" s="13" t="n"/>
+      <c r="T38" s="13" t="n"/>
+      <c r="U38" s="13" t="n"/>
+      <c r="V38" s="13" t="n"/>
+      <c r="W38" s="24" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="8" t="n"/>
@@ -3199,7 +3493,11 @@
       <c r="P39" s="9" t="n"/>
       <c r="Q39" s="9" t="n"/>
       <c r="R39" s="9" t="n"/>
-      <c r="S39" s="22" t="n"/>
+      <c r="S39" s="9" t="n"/>
+      <c r="T39" s="9" t="n"/>
+      <c r="U39" s="9" t="n"/>
+      <c r="V39" s="9" t="n"/>
+      <c r="W39" s="22" t="n"/>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="12" t="n"/>
@@ -3220,7 +3518,11 @@
       <c r="P40" s="13" t="n"/>
       <c r="Q40" s="13" t="n"/>
       <c r="R40" s="13" t="n"/>
-      <c r="S40" s="24" t="n"/>
+      <c r="S40" s="13" t="n"/>
+      <c r="T40" s="13" t="n"/>
+      <c r="U40" s="13" t="n"/>
+      <c r="V40" s="13" t="n"/>
+      <c r="W40" s="24" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="8" t="n"/>
@@ -3241,7 +3543,11 @@
       <c r="P41" s="9" t="n"/>
       <c r="Q41" s="9" t="n"/>
       <c r="R41" s="9" t="n"/>
-      <c r="S41" s="22" t="n"/>
+      <c r="S41" s="9" t="n"/>
+      <c r="T41" s="9" t="n"/>
+      <c r="U41" s="9" t="n"/>
+      <c r="V41" s="9" t="n"/>
+      <c r="W41" s="22" t="n"/>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="12" t="n"/>
@@ -3262,7 +3568,11 @@
       <c r="P42" s="13" t="n"/>
       <c r="Q42" s="13" t="n"/>
       <c r="R42" s="13" t="n"/>
-      <c r="S42" s="24" t="n"/>
+      <c r="S42" s="13" t="n"/>
+      <c r="T42" s="13" t="n"/>
+      <c r="U42" s="13" t="n"/>
+      <c r="V42" s="13" t="n"/>
+      <c r="W42" s="24" t="n"/>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="8" t="n"/>
@@ -3283,7 +3593,11 @@
       <c r="P43" s="9" t="n"/>
       <c r="Q43" s="9" t="n"/>
       <c r="R43" s="9" t="n"/>
-      <c r="S43" s="22" t="n"/>
+      <c r="S43" s="9" t="n"/>
+      <c r="T43" s="9" t="n"/>
+      <c r="U43" s="9" t="n"/>
+      <c r="V43" s="9" t="n"/>
+      <c r="W43" s="22" t="n"/>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="12" t="n"/>
@@ -3304,7 +3618,11 @@
       <c r="P44" s="13" t="n"/>
       <c r="Q44" s="13" t="n"/>
       <c r="R44" s="13" t="n"/>
-      <c r="S44" s="24" t="n"/>
+      <c r="S44" s="13" t="n"/>
+      <c r="T44" s="13" t="n"/>
+      <c r="U44" s="13" t="n"/>
+      <c r="V44" s="13" t="n"/>
+      <c r="W44" s="24" t="n"/>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="8" t="n"/>
@@ -3325,7 +3643,11 @@
       <c r="P45" s="9" t="n"/>
       <c r="Q45" s="9" t="n"/>
       <c r="R45" s="9" t="n"/>
-      <c r="S45" s="22" t="n"/>
+      <c r="S45" s="9" t="n"/>
+      <c r="T45" s="9" t="n"/>
+      <c r="U45" s="9" t="n"/>
+      <c r="V45" s="9" t="n"/>
+      <c r="W45" s="22" t="n"/>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="12" t="n"/>
@@ -3346,7 +3668,11 @@
       <c r="P46" s="13" t="n"/>
       <c r="Q46" s="13" t="n"/>
       <c r="R46" s="13" t="n"/>
-      <c r="S46" s="24" t="n"/>
+      <c r="S46" s="13" t="n"/>
+      <c r="T46" s="13" t="n"/>
+      <c r="U46" s="13" t="n"/>
+      <c r="V46" s="13" t="n"/>
+      <c r="W46" s="24" t="n"/>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="8" t="n"/>
@@ -3367,7 +3693,11 @@
       <c r="P47" s="9" t="n"/>
       <c r="Q47" s="9" t="n"/>
       <c r="R47" s="9" t="n"/>
-      <c r="S47" s="22" t="n"/>
+      <c r="S47" s="9" t="n"/>
+      <c r="T47" s="9" t="n"/>
+      <c r="U47" s="9" t="n"/>
+      <c r="V47" s="9" t="n"/>
+      <c r="W47" s="22" t="n"/>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="12" t="n"/>
@@ -3388,7 +3718,11 @@
       <c r="P48" s="13" t="n"/>
       <c r="Q48" s="13" t="n"/>
       <c r="R48" s="13" t="n"/>
-      <c r="S48" s="24" t="n"/>
+      <c r="S48" s="13" t="n"/>
+      <c r="T48" s="13" t="n"/>
+      <c r="U48" s="13" t="n"/>
+      <c r="V48" s="13" t="n"/>
+      <c r="W48" s="24" t="n"/>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="8" t="n"/>
@@ -3409,7 +3743,11 @@
       <c r="P49" s="9" t="n"/>
       <c r="Q49" s="9" t="n"/>
       <c r="R49" s="9" t="n"/>
-      <c r="S49" s="22" t="n"/>
+      <c r="S49" s="9" t="n"/>
+      <c r="T49" s="9" t="n"/>
+      <c r="U49" s="9" t="n"/>
+      <c r="V49" s="9" t="n"/>
+      <c r="W49" s="22" t="n"/>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="12" t="n"/>
@@ -3430,7 +3768,11 @@
       <c r="P50" s="13" t="n"/>
       <c r="Q50" s="13" t="n"/>
       <c r="R50" s="13" t="n"/>
-      <c r="S50" s="24" t="n"/>
+      <c r="S50" s="13" t="n"/>
+      <c r="T50" s="13" t="n"/>
+      <c r="U50" s="13" t="n"/>
+      <c r="V50" s="13" t="n"/>
+      <c r="W50" s="24" t="n"/>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="8" t="n"/>
@@ -3451,7 +3793,11 @@
       <c r="P51" s="9" t="n"/>
       <c r="Q51" s="9" t="n"/>
       <c r="R51" s="9" t="n"/>
-      <c r="S51" s="22" t="n"/>
+      <c r="S51" s="9" t="n"/>
+      <c r="T51" s="9" t="n"/>
+      <c r="U51" s="9" t="n"/>
+      <c r="V51" s="9" t="n"/>
+      <c r="W51" s="22" t="n"/>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="12" t="n"/>
@@ -3472,7 +3818,11 @@
       <c r="P52" s="13" t="n"/>
       <c r="Q52" s="13" t="n"/>
       <c r="R52" s="13" t="n"/>
-      <c r="S52" s="24" t="n"/>
+      <c r="S52" s="13" t="n"/>
+      <c r="T52" s="13" t="n"/>
+      <c r="U52" s="13" t="n"/>
+      <c r="V52" s="13" t="n"/>
+      <c r="W52" s="24" t="n"/>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="8" t="n"/>
@@ -3493,7 +3843,11 @@
       <c r="P53" s="9" t="n"/>
       <c r="Q53" s="9" t="n"/>
       <c r="R53" s="9" t="n"/>
-      <c r="S53" s="22" t="n"/>
+      <c r="S53" s="9" t="n"/>
+      <c r="T53" s="9" t="n"/>
+      <c r="U53" s="9" t="n"/>
+      <c r="V53" s="9" t="n"/>
+      <c r="W53" s="22" t="n"/>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="12" t="n"/>
@@ -3514,7 +3868,11 @@
       <c r="P54" s="13" t="n"/>
       <c r="Q54" s="13" t="n"/>
       <c r="R54" s="13" t="n"/>
-      <c r="S54" s="24" t="n"/>
+      <c r="S54" s="13" t="n"/>
+      <c r="T54" s="13" t="n"/>
+      <c r="U54" s="13" t="n"/>
+      <c r="V54" s="13" t="n"/>
+      <c r="W54" s="24" t="n"/>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="8" t="n"/>
@@ -3535,7 +3893,11 @@
       <c r="P55" s="9" t="n"/>
       <c r="Q55" s="9" t="n"/>
       <c r="R55" s="9" t="n"/>
-      <c r="S55" s="22" t="n"/>
+      <c r="S55" s="9" t="n"/>
+      <c r="T55" s="9" t="n"/>
+      <c r="U55" s="9" t="n"/>
+      <c r="V55" s="9" t="n"/>
+      <c r="W55" s="22" t="n"/>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="12" t="n"/>
@@ -3556,7 +3918,11 @@
       <c r="P56" s="13" t="n"/>
       <c r="Q56" s="13" t="n"/>
       <c r="R56" s="13" t="n"/>
-      <c r="S56" s="24" t="n"/>
+      <c r="S56" s="13" t="n"/>
+      <c r="T56" s="13" t="n"/>
+      <c r="U56" s="13" t="n"/>
+      <c r="V56" s="13" t="n"/>
+      <c r="W56" s="24" t="n"/>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="8" t="n"/>
@@ -3577,14 +3943,18 @@
       <c r="P57" s="9" t="n"/>
       <c r="Q57" s="9" t="n"/>
       <c r="R57" s="9" t="n"/>
-      <c r="S57" s="22" t="n"/>
+      <c r="S57" s="9" t="n"/>
+      <c r="T57" s="9" t="n"/>
+      <c r="U57" s="9" t="n"/>
+      <c r="V57" s="9" t="n"/>
+      <c r="W57" s="22" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
   <mergeCells count="3">
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="A1:S1"/>
-    <mergeCell ref="A2:P2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="A1:W1"/>
+    <mergeCell ref="A2:T2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="P5:P28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_소프트웨어팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_소프트웨어팀_입력_2026.xlsx
@@ -66,7 +66,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -121,6 +121,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00B08F36"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000277BD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EF6C00"/>
       </patternFill>
     </fill>
   </fills>
@@ -237,7 +247,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -569,6 +579,21 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1450,7 +1475,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="109" t="inlineStr">
+      <c r="A1" s="112" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 소프트웨어팀 │ 2026</t>
         </is>
@@ -1479,7 +1504,7 @@
       <c r="W1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="110" t="inlineStr">
+      <c r="A2" s="113" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 소프트웨어팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1503,9 +1528,9 @@
       <c r="R2" s="16" t="n"/>
       <c r="S2" s="16" t="n"/>
       <c r="T2" s="17" t="n"/>
-      <c r="U2" s="111" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 14:35</t>
+      <c r="U2" s="114" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 15:15</t>
         </is>
       </c>
       <c r="V2" s="16" t="n"/>
@@ -1684,45 +1709,45 @@
           <t>부서진척률(%)</t>
         </is>
       </c>
-      <c r="L4" s="7" t="inlineStr">
+      <c r="L4" s="115" t="inlineStr">
         <is>
           <t>검토</t>
         </is>
       </c>
-      <c r="M4" s="70" t="inlineStr">
+      <c r="M4" s="115" t="inlineStr">
         <is>
           <t>예정일</t>
         </is>
       </c>
-      <c r="N4" s="7" t="inlineStr">
+      <c r="N4" s="116" t="inlineStr">
         <is>
           <t>프로
 그램</t>
         </is>
       </c>
-      <c r="O4" s="70" t="inlineStr">
+      <c r="O4" s="116" t="inlineStr">
         <is>
           <t>예정일</t>
         </is>
       </c>
-      <c r="P4" s="7" t="inlineStr">
+      <c r="P4" s="115" t="inlineStr">
         <is>
           <t>DRY
 RUN</t>
         </is>
       </c>
-      <c r="Q4" s="70" t="inlineStr">
+      <c r="Q4" s="115" t="inlineStr">
         <is>
           <t>예정일</t>
         </is>
       </c>
-      <c r="R4" s="7" t="inlineStr">
+      <c r="R4" s="116" t="inlineStr">
         <is>
           <t>AUTO
 RUN</t>
         </is>
       </c>
-      <c r="S4" s="70" t="inlineStr">
+      <c r="S4" s="116" t="inlineStr">
         <is>
           <t>예정일</t>
         </is>
